--- a/Sunday_Arrivals.xlsx
+++ b/Sunday_Arrivals.xlsx
@@ -426,16 +426,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Council</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>21/06</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>28/06</t>
         </is>
@@ -447,11 +457,16 @@
           <t>Colossians 1</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Isaac Agyeman</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
         <v>143</v>
       </c>
-      <c r="C2" t="n">
-        <v>0</v>
+      <c r="D2" t="n">
+        <v>96</v>
       </c>
     </row>
     <row r="3">
@@ -460,11 +475,16 @@
           <t>Colossians 2</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Edwin Ogoe</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
         <v>83</v>
       </c>
-      <c r="C3" t="n">
-        <v>0</v>
+      <c r="D3" t="n">
+        <v>93</v>
       </c>
     </row>
     <row r="4">
@@ -473,11 +493,16 @@
           <t>Colossians 3</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Nathan Kudowor</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
         <v>64</v>
       </c>
-      <c r="C4" t="n">
-        <v>0</v>
+      <c r="D4" t="n">
+        <v>43</v>
       </c>
     </row>
     <row r="5">
@@ -486,11 +511,11 @@
           <t>Colossians Total</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="C5" t="n">
         <v>290</v>
       </c>
-      <c r="C5" t="n">
-        <v>0</v>
+      <c r="D5" t="n">
+        <v>232</v>
       </c>
     </row>
     <row r="7">
@@ -499,11 +524,16 @@
           <t>Galatians 1</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Isaac Agyeman</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
         <v>38</v>
       </c>
-      <c r="C7" t="n">
-        <v>0</v>
+      <c r="D7" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="8">
@@ -512,11 +542,16 @@
           <t>Galatians 2</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Richmond Annan</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
         <v>158</v>
       </c>
-      <c r="C8" t="n">
-        <v>0</v>
+      <c r="D8" t="n">
+        <v>128</v>
       </c>
     </row>
     <row r="9">
@@ -525,10 +560,15 @@
           <t>Galatians 2 (Hold)</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0</v>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Edwin Ogoe</t>
+        </is>
       </c>
       <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -538,11 +578,16 @@
           <t>Galatians 4</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Eric Boachie Yiadom</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
         <v>100</v>
       </c>
-      <c r="C10" t="n">
-        <v>0</v>
+      <c r="D10" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="11">
@@ -551,11 +596,16 @@
           <t>Galatians 5</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Michael Oteng</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
         <v>157</v>
       </c>
-      <c r="C11" t="n">
-        <v>0</v>
+      <c r="D11" t="n">
+        <v>116</v>
       </c>
     </row>
     <row r="12">
@@ -564,11 +614,16 @@
           <t>Galatians 8</t>
         </is>
       </c>
-      <c r="B12" t="n">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Caleb Osei-Kofi</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
         <v>137</v>
       </c>
-      <c r="C12" t="n">
-        <v>0</v>
+      <c r="D12" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="13">
@@ -577,11 +632,16 @@
           <t>Galatians 9</t>
         </is>
       </c>
-      <c r="B13" t="n">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Divine Olubakinde</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
         <v>87</v>
       </c>
-      <c r="C13" t="n">
-        <v>0</v>
+      <c r="D13" t="n">
+        <v>65</v>
       </c>
     </row>
     <row r="14">
@@ -590,11 +650,11 @@
           <t>Galatians Total</t>
         </is>
       </c>
-      <c r="B14" t="n">
+      <c r="C14" t="n">
         <v>677</v>
       </c>
-      <c r="C14" t="n">
-        <v>0</v>
+      <c r="D14" t="n">
+        <v>507</v>
       </c>
     </row>
     <row r="16">
@@ -603,11 +663,16 @@
           <t>Galatians 3</t>
         </is>
       </c>
-      <c r="B16" t="n">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Joseph Teye</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
         <v>99</v>
       </c>
-      <c r="C16" t="n">
-        <v>0</v>
+      <c r="D16" t="n">
+        <v>79</v>
       </c>
     </row>
     <row r="17">
@@ -616,11 +681,16 @@
           <t>Galatians 6 A</t>
         </is>
       </c>
-      <c r="B17" t="n">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Nana Kofi Danso-Mensah</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
         <v>121</v>
       </c>
-      <c r="C17" t="n">
-        <v>0</v>
+      <c r="D17" t="n">
+        <v>94</v>
       </c>
     </row>
     <row r="18">
@@ -629,11 +699,16 @@
           <t>Galatians 7</t>
         </is>
       </c>
-      <c r="B18" t="n">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Albert Gillies Heward-Mills</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
         <v>206</v>
       </c>
-      <c r="C18" t="n">
-        <v>0</v>
+      <c r="D18" t="n">
+        <v>144</v>
       </c>
     </row>
     <row r="19">
@@ -642,11 +717,11 @@
           <t>Jesus Night Total</t>
         </is>
       </c>
-      <c r="B19" t="n">
+      <c r="C19" t="n">
         <v>426</v>
       </c>
-      <c r="C19" t="n">
-        <v>0</v>
+      <c r="D19" t="n">
+        <v>317</v>
       </c>
     </row>
     <row r="21">
@@ -655,11 +730,11 @@
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B21" t="n">
+      <c r="C21" t="n">
         <v>1393</v>
       </c>
-      <c r="C21" t="n">
-        <v>0</v>
+      <c r="D21" t="n">
+        <v>1056</v>
       </c>
     </row>
   </sheetData>
@@ -713,7 +788,7 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -731,7 +806,7 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -749,7 +824,7 @@
         <v>16</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
@@ -785,7 +860,7 @@
         <v>36</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
@@ -803,7 +878,7 @@
         <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -839,7 +914,7 @@
         <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
@@ -857,7 +932,7 @@
         <v>26</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11">
@@ -875,7 +950,7 @@
         <v>28</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
@@ -893,15 +968,20 @@
         <v>15</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
       <c r="C13" t="n">
         <v>157</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -955,7 +1035,7 @@
         <v>14</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -973,7 +1053,7 @@
         <v>16</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -991,7 +1071,7 @@
         <v>14</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
@@ -1009,7 +1089,7 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -1027,7 +1107,7 @@
         <v>14</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
@@ -1045,7 +1125,7 @@
         <v>16</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
@@ -1063,7 +1143,7 @@
         <v>26</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9">
@@ -1081,7 +1161,7 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -1099,15 +1179,20 @@
         <v>7</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
       <c r="C11" t="n">
         <v>121</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -1161,7 +1246,7 @@
         <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -1215,7 +1300,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -1233,7 +1318,7 @@
         <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -1269,7 +1354,7 @@
         <v>35</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9">
@@ -1287,7 +1372,7 @@
         <v>31</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10">
@@ -1305,7 +1390,7 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -1323,7 +1408,7 @@
         <v>54</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -1341,7 +1426,7 @@
         <v>14</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
@@ -1359,7 +1444,7 @@
         <v>29</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14">
@@ -1377,7 +1462,7 @@
         <v>12</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
@@ -1395,7 +1480,7 @@
         <v>8</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16">
@@ -1417,11 +1502,16 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
       <c r="C17" t="n">
         <v>206</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -1475,7 +1565,7 @@
         <v>17</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -1493,7 +1583,7 @@
         <v>36</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
@@ -1529,7 +1619,7 @@
         <v>20</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -1547,7 +1637,7 @@
         <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
@@ -1565,7 +1655,7 @@
         <v>41</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8">
@@ -1583,15 +1673,20 @@
         <v>15</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
       <c r="C9" t="n">
         <v>137</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -1645,7 +1740,7 @@
         <v>24</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
@@ -1663,7 +1758,7 @@
         <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -1681,7 +1776,7 @@
         <v>13</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -1717,7 +1812,7 @@
         <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -1735,7 +1830,7 @@
         <v>15</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -1753,15 +1848,20 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
       <c r="C9" t="n">
         <v>87</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -1833,7 +1933,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -1851,7 +1951,7 @@
         <v>28</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
@@ -1869,7 +1969,7 @@
         <v>15</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">
@@ -1905,7 +2005,7 @@
         <v>14</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -1923,7 +2023,7 @@
         <v>22</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9">
@@ -1941,7 +2041,7 @@
         <v>12</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
@@ -1959,7 +2059,7 @@
         <v>12</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -1977,7 +2077,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
@@ -1995,15 +2095,20 @@
         <v>14</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
       <c r="C13" t="n">
         <v>143</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -2111,7 +2216,7 @@
         <v>52</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6">
@@ -2129,7 +2234,7 @@
         <v>16</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
@@ -2183,15 +2288,20 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
       <c r="C10" t="n">
         <v>83</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -2245,7 +2355,7 @@
         <v>13</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -2263,7 +2373,7 @@
         <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -2281,7 +2391,7 @@
         <v>20</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
@@ -2317,15 +2427,20 @@
         <v>20</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
       <c r="C7" t="n">
         <v>64</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -2379,7 +2494,7 @@
         <v>20</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
@@ -2397,15 +2512,20 @@
         <v>18</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
       <c r="C4" t="n">
         <v>38</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -2477,7 +2597,7 @@
         <v>18</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4">
@@ -2495,7 +2615,7 @@
         <v>22</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
@@ -2513,7 +2633,7 @@
         <v>16</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6">
@@ -2531,7 +2651,7 @@
         <v>36</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7">
@@ -2549,7 +2669,7 @@
         <v>12</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
@@ -2567,7 +2687,7 @@
         <v>31</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
@@ -2585,7 +2705,7 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -2603,15 +2723,20 @@
         <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
       <c r="C11" t="n">
         <v>158</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>
@@ -2651,6 +2776,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
@@ -2709,7 +2839,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -2745,7 +2875,7 @@
         <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -2763,7 +2893,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
@@ -2781,7 +2911,7 @@
         <v>37</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7">
@@ -2799,15 +2929,20 @@
         <v>47</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
       <c r="C8" t="n">
         <v>99</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -2861,7 +2996,7 @@
         <v>27</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
@@ -2879,7 +3014,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -2897,7 +3032,7 @@
         <v>25</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5">
@@ -2915,7 +3050,7 @@
         <v>48</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6">
@@ -2937,11 +3072,16 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
       <c r="C7" t="n">
         <v>100</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/Sunday_Arrivals.xlsx
+++ b/Sunday_Arrivals.xlsx
@@ -11,16 +11,18 @@
     <sheet name="Colossians 1" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Colossians 2" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Colossians 3" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Galatians 1" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Galatians 2" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Galatians 2 (Hold)" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Galatians 3" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Galatians 4" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Galatians 5" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Galatians 6 A" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Galatians 7" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Galatians 8" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Galatians 9" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Colossians 4" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Colossians 5" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Galatians 1" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Galatians 2" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Galatians 2 (Hold)" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Galatians 3" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Galatians 4" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Galatians 5" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Galatians 6 A" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Galatians 7" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Galatians 8" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Galatians 9" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,12 +444,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>21/06</t>
+          <t>28/06</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>28/06</t>
+          <t>05/07</t>
         </is>
       </c>
     </row>
@@ -463,10 +465,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>143</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>96</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
@@ -481,10 +483,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="D3" t="n">
-        <v>93</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4">
@@ -495,246 +497,282 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Nathan Kudowor</t>
+          <t>Michael Sarpong</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="D4" t="n">
-        <v>43</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Colossians Total</t>
+          <t>Colossians 4</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Malcolm Otchere - Forbih</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>290</v>
+        <v>43</v>
       </c>
       <c r="D5" t="n">
-        <v>232</v>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Colossians 5</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Abraham Koney</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>51</v>
+      </c>
+      <c r="D6" t="n">
+        <v>59</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Galatians 1</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Isaac Agyeman</t>
+          <t>Colossians Total</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>38</v>
+        <v>232</v>
       </c>
       <c r="D7" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Galatians 2</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Richmond Annan</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>158</v>
-      </c>
-      <c r="D8" t="n">
-        <v>128</v>
+        <v>230</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Galatians 2 (Hold)</t>
+          <t>Galatians 1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Edwin Ogoe</t>
+          <t>Isaac Agyeman</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Galatians 4</t>
+          <t>Galatians 2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Eric Boachie Yiadom</t>
+          <t>Richmond Annan</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="D10" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Galatians 5</t>
+          <t>Galatians 2 (Hold)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Michael Oteng</t>
+          <t>Edwin Ogoe</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>116</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Galatians 8</t>
+          <t>Galatians 4</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Caleb Osei-Kofi</t>
+          <t>Eric Boachie Yiadom</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>137</v>
+        <v>80</v>
       </c>
       <c r="D12" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Galatians 9</t>
+          <t>Galatians 5</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Divine Olubakinde</t>
+          <t>Michael Oteng</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>87</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
-        <v>65</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Galatians Total</t>
+          <t>Galatians 8</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Caleb Osei-Kofi</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>677</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
-        <v>507</v>
+        <v>85</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Galatians 9</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Divine Olubakinde</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>65</v>
+      </c>
+      <c r="D15" t="n">
+        <v>54</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Galatians 3</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Joseph Teye</t>
+          <t>Galatians Total</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>99</v>
+        <v>515</v>
       </c>
       <c r="D16" t="n">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Galatians 6 A</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Nana Kofi Danso-Mensah</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>121</v>
-      </c>
-      <c r="D17" t="n">
-        <v>94</v>
+        <v>398</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Galatians 7</t>
+          <t>Galatians 3</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Albert Gillies Heward-Mills</t>
+          <t>Joseph Teye</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>206</v>
+        <v>79</v>
       </c>
       <c r="D18" t="n">
-        <v>144</v>
+        <v>64</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Jesus Night Total</t>
+          <t>Galatians 6 A</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Nana Kofi Danso-Mensah</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>426</v>
+        <v>99</v>
       </c>
       <c r="D19" t="n">
-        <v>317</v>
+        <v>164</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Galatians 7</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Albert Gillies Heward-Mills</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>144</v>
+      </c>
+      <c r="D20" t="n">
+        <v>150</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>Jesus Night Total</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>322</v>
+      </c>
+      <c r="D21" t="n">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="C21" t="n">
-        <v>1393</v>
-      </c>
-      <c r="D21" t="n">
-        <v>1056</v>
+      <c r="C23" t="n">
+        <v>1069</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1006</v>
       </c>
     </row>
   </sheetData>
@@ -748,7 +786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -764,224 +802,152 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>21/06</t>
+          <t>28/06</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>28/06</t>
+          <t>05/07</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AIT</t>
+          <t>Campus Anagkazo</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Lawrence Adetunji</t>
+          <t>Nayram Gblorkpor</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AIT Yeshua</t>
+          <t>Limann</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Jonathan Ekhagbai</t>
+          <t>Kwesi Boadu-Amoama</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Aparche</t>
+          <t>Mensah Sarbah Poimen</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cyrus-Dag Stephens</t>
+          <t>Prince Okai</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Encephal College of Health</t>
+          <t>Prince of Peace New</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Samuel Tigah</t>
+          <t>Joseph Akyem</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Galilea</t>
+          <t>Revelations</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Lady Vanessa Osei</t>
+          <t>Edna Adorshie</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GTUC</t>
+          <t>Sarbah</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Richard Manu</t>
+          <t>Joseph Teye</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GTUC Allos</t>
+          <t>Sey</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Michael Oteng</t>
+          <t>Dennis Kpogli</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GTUC Allos 3</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Sylvester Ntumy</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>79</v>
       </c>
       <c r="D9" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>GTUC Main Campus</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Jeremiah Ashong</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>26</v>
-      </c>
-      <c r="D10" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Kings/Regent</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Prince Forson</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>28</v>
-      </c>
-      <c r="D11" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Korle Bu Light</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Sonia Elolo</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>15</v>
-      </c>
-      <c r="D12" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>157</v>
-      </c>
-      <c r="D13" t="n">
-        <v>116</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -995,7 +961,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1011,188 +977,116 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>21/06</t>
+          <t>28/06</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>28/06</t>
+          <t>05/07</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Bani</t>
+          <t>UPSA Campus Hostels</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kojo Afriyie</t>
+          <t>Andrew Heward-Mills</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Block A Annex</t>
+          <t>Upsa Diaspora</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Marcia Adomako</t>
+          <t>Bright Nurtey Tettey Tetteh</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Commonwealth</t>
+          <t>UPSA Green Hostel</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Peter Tefuttor</t>
+          <t>Desmond Hlorgbey</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Evandy</t>
+          <t>UPSA Hostels A &amp; B</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Delali Apedu</t>
+          <t>Jayson Quarshie</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Pent B</t>
+          <t>UPSA Rawlings Hostel</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Yves Mensah</t>
+          <t>Eric Boachie Yiadom</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Pent C</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Roland Cudjoe</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16</v>
+        <v>80</v>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Pent Old &amp; A</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Nana Kofi Danso-Mensah</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>26</v>
-      </c>
-      <c r="D8" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>TF</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Elizabeth Obeng Adu</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>3</v>
-      </c>
-      <c r="D9" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Volta</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Stephanie Seglah</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>7</v>
-      </c>
-      <c r="D10" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>121</v>
-      </c>
-      <c r="D11" t="n">
-        <v>94</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -1206,7 +1100,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1222,296 +1116,224 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>21/06</t>
+          <t>28/06</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>28/06</t>
+          <t>05/07</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Area 1  Logos</t>
+          <t>AIT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Erasmus Laryea</t>
+          <t>Lawrence Adetunji</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Commonwealth 1</t>
+          <t>AIT Yeshua</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Lois Osei</t>
+          <t>Jonathan Ekhagbai</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Diamond Jubilee 1</t>
+          <t>Aparche</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Deborah Wiredu</t>
+          <t>Cyrus-Dag Stephens</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Diamond Jubilee 2</t>
+          <t>Encephal College of Health</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Abena Kyeremaa</t>
+          <t>Samuel Tigah</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Kwapong</t>
+          <t>Galilea</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Eunice Owusu</t>
+          <t>Lady Vanessa Osei</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Legon Hall</t>
+          <t>GTUC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Edberg Ayensu</t>
+          <t>Richard Manu</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Main Campus Allos</t>
+          <t>GTUC Allos</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Albert Gillies Heward-Mills</t>
+          <t>Michael Oteng</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>33</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Main Campus Charis</t>
+          <t>GTUC Allos 3</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Stephen Asare Osei</t>
+          <t>Sylvester Ntumy</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="D9" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Main Campus Dunamis</t>
+          <t>GTUC Main Campus</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Nana Kwame Barima</t>
+          <t>Jeremiah Ashong</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Main Campus Hagios</t>
+          <t>Kings/Regent</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Philmorra Laryea Okorley</t>
+          <t>Prince Forson</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>54</v>
+        <v>12</v>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Main Campus Parakletos</t>
+          <t>Korle Bu Light</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Melissa Meledi</t>
+          <t>Sonia Elolo</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Main Campus Pistis</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Richard Mawuli Sogbo</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>29</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Main Campus Proskuneo</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Isaac Baidoo</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>12</v>
-      </c>
-      <c r="D14" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Main Campus Tsalach</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Jennifer Aidoo</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>8</v>
-      </c>
-      <c r="D15" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Main campus Zogreo</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Elinam Fiagbe</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>206</v>
-      </c>
-      <c r="D17" t="n">
-        <v>144</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -1525,7 +1347,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1541,152 +1363,296 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>21/06</t>
+          <t>28/06</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>28/06</t>
+          <t>05/07</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AKUAFO</t>
+          <t>Akuafo New</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Foanor Alloh</t>
+          <t>Karyn Tagoe</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Akuafo Zoe</t>
+          <t>Bani</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Enoch Bentil</t>
+          <t>Kojo Afriyie</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ELU</t>
+          <t>Block A Annex</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tracy Osei</t>
+          <t>Marcia Adomako</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Legon hall</t>
+          <t>Block B Annex New</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Nana Ahema Forson</t>
+          <t>Kevin Brown</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Legon Hall B</t>
+          <t>Commonwealth</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Yosi Forson</t>
+          <t>Peter Tefuttor</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Volta</t>
+          <t>Diamond Jubilee</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Caleb Osei-Kofi</t>
+          <t>Emelda Antwi-Agyei</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>35</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Volta Mega</t>
+          <t>Evandy</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Doris Ainooh</t>
+          <t>Delali Apedu</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Evandy Annex New</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Caroline Hammond</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Pent B</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Yves Mensah</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>10</v>
+      </c>
+      <c r="D10" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Pent C</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Roland Cudjoe</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>16</v>
+      </c>
+      <c r="D11" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Pent Old &amp; A</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Nana Kofi Danso-Mensah</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>18</v>
+      </c>
+      <c r="D12" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Elizabeth Obeng Adu</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TF Annex New</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Samuel Boateng</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Volta</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Stephanie Seglah</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>9</v>
+      </c>
+      <c r="D15" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Volta Annex New</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Esllah Osei</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C9" t="n">
-        <v>137</v>
-      </c>
-      <c r="D9" t="n">
-        <v>90</v>
+      <c r="C17" t="n">
+        <v>99</v>
+      </c>
+      <c r="D17" t="n">
+        <v>164</v>
       </c>
     </row>
   </sheetData>
@@ -1700,7 +1666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1716,36 +1682,674 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>21/06</t>
+          <t>28/06</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>28/06</t>
+          <t>05/07</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>UPSA Allos 1</t>
+          <t>Akuafo Charis</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Papa Kojo Amoakwa</t>
+          <t>Stephen Asare Osei</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>Akuafo Hall 1 New</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Fredrick Anokye</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Akuafo Hall 2 New</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Dacosta Amponsah</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Area 1  Logos</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Erasmus Laryea</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>8</v>
+      </c>
+      <c r="D5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Commonwealth 1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Lois Osei</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Commonwealth 2 New</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>David Arhin</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Diamond Jubilee 1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Deborah Wiredu</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Diamond Jubilee 2</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Abena Kyeremaa</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Jesus Night TF New</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Jochebed Lawson-Heymann</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Kwapong</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Eunice Owusu</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Legon Hall</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Edberg Ayensu</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Main Campus Allos</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Albert Gillies Heward-Mills</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>33</v>
+      </c>
+      <c r="D13" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Main Campus Dunamis</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Nana Kwame Barima</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>10</v>
+      </c>
+      <c r="D14" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Main Campus Hagios</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Philmorra Laryea Okorley</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Main Campus Parakletos</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Melissa Meledi</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>11</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Main Campus Pistis</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Richard Mawuli Sogbo</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>18</v>
+      </c>
+      <c r="D17" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Main Campus Proskuneo</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Isaac Baidoo</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>17</v>
+      </c>
+      <c r="D18" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Main Campus Tsalach</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Jennifer Aidoo</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>16</v>
+      </c>
+      <c r="D19" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Main campus Zogreo</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Elinam Fiagbe</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Sey New</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Frank Anokye</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Volta Hall</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Precious Antwi</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>144</v>
+      </c>
+      <c r="D23" t="n">
+        <v>150</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>28/06</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>05/07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>AKUAFO</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Foanor Alloh</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>14</v>
+      </c>
+      <c r="D2" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Akuafo Hall 6</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ruby Nelson</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Akuafo Zoe</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Enoch Bentil</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>17</v>
+      </c>
+      <c r="D4" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ELU</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Tracy Osei</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Legon hall</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Nana Ahema Forson</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Legon Hall B</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Yosi Forson</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>11</v>
+      </c>
+      <c r="D7" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Volta</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Caleb Osei-Kofi</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>35</v>
+      </c>
+      <c r="D8" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Volta Mega</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Doris Ainooh</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>8</v>
+      </c>
+      <c r="D9" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Volta Others</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Rachael Sekyiwaaa</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>90</v>
+      </c>
+      <c r="D11" t="n">
+        <v>85</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>28/06</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>05/07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>UPSA Allos 1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Papa Kojo Amoakwa</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>30</v>
+      </c>
+      <c r="D2" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>UPSA Allos 2</t>
         </is>
       </c>
@@ -1755,7 +2359,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
         <v>11</v>
@@ -1773,10 +2377,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -1809,10 +2413,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -1827,10 +2431,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -1845,23 +2449,59 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D8" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>UPSA Allos 8</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Divine Olubakinde</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>UPSA Allos 9</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Chris Keelson</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C9" t="n">
-        <v>87</v>
-      </c>
-      <c r="D9" t="n">
+      <c r="C11" t="n">
         <v>65</v>
+      </c>
+      <c r="D11" t="n">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -1875,7 +2515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1891,12 +2531,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>21/06</t>
+          <t>28/06</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>28/06</t>
+          <t>05/07</t>
         </is>
       </c>
     </row>
@@ -1912,10 +2552,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -1930,185 +2570,23 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Haatso Mabey</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Malcolm Otchere - Forbih</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Hatso TBC</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Zenas Adarkwah Yiadom</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>15</v>
-      </c>
-      <c r="D5" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Pantang Campus</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Princess Gueyennevievarl Wilson-Anderson</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Pantang Town</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Abraham Koney</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>14</v>
-      </c>
-      <c r="D7" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>THS Agbogba</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Raymond Agboola</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>22</v>
-      </c>
-      <c r="D8" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>THS Bohye</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Christian Ocquaye</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>12</v>
-      </c>
-      <c r="D9" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>THS Ecomog</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Alex Baah-Gyambrah</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>12</v>
-      </c>
-      <c r="D10" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Wisconsin</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Samuel Umerah</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>5</v>
-      </c>
-      <c r="D11" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Wisconsin Fruitful</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Thomas Dodoo</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>14</v>
-      </c>
-      <c r="D12" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>143</v>
-      </c>
-      <c r="D13" t="n">
-        <v>96</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -2122,7 +2600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2138,12 +2616,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>21/06</t>
+          <t>28/06</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>28/06</t>
+          <t>05/07</t>
         </is>
       </c>
     </row>
@@ -2213,10 +2691,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D5" t="n">
-        <v>54</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6">
@@ -2231,10 +2709,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D6" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -2285,23 +2763,41 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D9" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Taifa Burkina</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Samuel Brown</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C10" t="n">
-        <v>83</v>
-      </c>
-      <c r="D10" t="n">
+      <c r="C11" t="n">
         <v>93</v>
+      </c>
+      <c r="D11" t="n">
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -2315,7 +2811,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2331,12 +2827,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>21/06</t>
+          <t>28/06</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>28/06</t>
+          <t>05/07</t>
         </is>
       </c>
     </row>
@@ -2352,7 +2848,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
         <v>9</v>
@@ -2370,39 +2866,39 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Haatso West</t>
+          <t>Haatso Executive</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Michael Sarpong</t>
+          <t>Stephen Mensah</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Kissieman</t>
+          <t>Haatso Melcom</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Oliver Agbenyegah</t>
+          <t>Kenneth Koomson</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -2415,32 +2911,68 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>THS Westland</t>
+          <t>Haatso Palace</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Joseph Halivor</t>
+          <t>Richard Anku</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Haatso West</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Michael Sarpong</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>12</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>THS Westland</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Joseph Halivor</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>15</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>64</v>
-      </c>
-      <c r="D7" t="n">
+      <c r="C9" t="n">
         <v>43</v>
+      </c>
+      <c r="D9" t="n">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -2454,7 +2986,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2470,62 +3002,80 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>21/06</t>
+          <t>28/06</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>28/06</t>
+          <t>05/07</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ACM</t>
+          <t>Haatso Mabey</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Nii Nkunim Armar</t>
+          <t>Malcolm Otchere - Forbih</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ACM 2</t>
+          <t>Hatso TBC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Daniel Orleans-Lindsay</t>
+          <t>Zenas Adarkwah Yiadom</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>THS Ecomog</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Alex Baah-Gyambrah</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>38</v>
-      </c>
-      <c r="D4" t="n">
-        <v>28</v>
+      <c r="C5" t="n">
+        <v>43</v>
+      </c>
+      <c r="D5" t="n">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -2539,7 +3089,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2555,24 +3105,24 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>21/06</t>
+          <t>28/06</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>28/06</t>
+          <t>05/07</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Adabraka</t>
+          <t>Pantang Campus</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Prince Agbesi</t>
+          <t>Princess Gueyennevievarl Wilson-Anderson</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -2585,158 +3135,104 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Arena</t>
+          <t>Pantang Town</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Zephaniah Lartey</t>
+          <t>Abraham Koney</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ATU Church</t>
+          <t>THS Agbogba</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>James Pekyie</t>
+          <t>Raymond Agboola</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ATU Main Campus</t>
+          <t>THS Bohye</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Racheal Boamah</t>
+          <t>Christian Ocquaye</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>City Campus</t>
+          <t>Wisconsin</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Abednego Abbey</t>
+          <t>Samuel Umerah</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="D6" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Jamestown</t>
+          <t>Wisconsin Fruitful</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Joel Quartey</t>
+          <t>Thomas Dodoo</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Jamestown Allos</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Ishmael Oplerm</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D8" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>UssherFort</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Seth Kpelebe</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>15</v>
-      </c>
-      <c r="D9" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Yours and Ours</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Emmanuel Otiboe</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>8</v>
-      </c>
-      <c r="D10" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>158</v>
-      </c>
-      <c r="D11" t="n">
-        <v>128</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -2750,7 +3246,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2766,26 +3262,80 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>21/06</t>
+          <t>28/06</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>28/06</t>
+          <t>05/07</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>ACM</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Nii Nkunim Armar</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>18</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ACM 2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Daniel Orleans-Lindsay</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ACM 3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Joan Obakpolor</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
+      <c r="C5" t="n">
+        <v>28</v>
+      </c>
+      <c r="D5" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -2799,7 +3349,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2815,42 +3365,42 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>21/06</t>
+          <t>28/06</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>28/06</t>
+          <t>05/07</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Campus Anagkazo</t>
+          <t>Accra City</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Nayram Gblorkpor</t>
+          <t>Ferdinand Adams</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Limann Governorship</t>
+          <t>Adabraka</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Gerald Essuman</t>
+          <t>Prince Agbesi</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -2863,86 +3413,176 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Main Campus Poimen</t>
+          <t>Arena</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Theodora Waguena</t>
+          <t>Zephaniah Lartey</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Mensah Sarbah Poimen</t>
+          <t>Arena Allos</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Prince Okai</t>
+          <t>Eric Akoto</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sarbah</t>
+          <t>ATU Church</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Joseph Teye</t>
+          <t>James Pekyie</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="D6" t="n">
-        <v>33</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sey</t>
+          <t>ATU Main Campus</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Dennis Kpogli</t>
+          <t>Racheal Boamah</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>City Campus</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Abednego Abbey</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>30</v>
+      </c>
+      <c r="D8" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Jamestown</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Joel Quartey</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>12</v>
+      </c>
+      <c r="D9" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Jamestown Allos</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ishmael Oplerm</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>UssherFort</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Seth Kpelebe</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>10</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Yours and Ours</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Emmanuel Otiboe</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>10</v>
+      </c>
+      <c r="D12" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C8" t="n">
-        <v>99</v>
-      </c>
-      <c r="D8" t="n">
-        <v>79</v>
+      <c r="C13" t="n">
+        <v>136</v>
+      </c>
+      <c r="D13" t="n">
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -2956,7 +3596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2972,116 +3612,26 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>21/06</t>
+          <t>28/06</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>28/06</t>
+          <t>05/07</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>UPSA Campus Hostels</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Andrew Heward-Mills</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Upsa Diaspora</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Bright Nurtey Tettey Tetteh</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>UPSA Green Hostel</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Desmond Hlorgbey</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>25</v>
-      </c>
-      <c r="D4" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>UPSA Hostels A &amp; B</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Jayson Quarshie</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>48</v>
-      </c>
-      <c r="D5" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>UPSA Rawlings Hostel</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Eric Boachie Yiadom</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>100</v>
-      </c>
-      <c r="D7" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Sunday_Arrivals.xlsx
+++ b/Sunday_Arrivals.xlsx
@@ -14,15 +14,16 @@
     <sheet name="Colossians 4" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Colossians 5" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Galatians 1" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Galatians 2" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Galatians 2 (Hold)" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Galatians 3" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Galatians 4" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Galatians 5" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Galatians 6 A" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Galatians 7" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Galatians 8" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Galatians 9" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Galatians 10" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Galatians 2" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Galatians 2 (Hold)" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Galatians 3" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Galatians 4" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Galatians 5" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Galatians 6 A" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Galatians 7" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Galatians 8" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Galatians 9" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,12 +445,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>28/06</t>
+          <t>05/07</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>05/07</t>
+          <t>12/07</t>
         </is>
       </c>
     </row>
@@ -465,10 +466,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="D2" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
@@ -483,10 +484,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="D3" t="n">
-        <v>85</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4">
@@ -501,10 +502,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D4" t="n">
-        <v>17</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5">
@@ -519,10 +520,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D5" t="n">
-        <v>48</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6">
@@ -537,10 +538,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="D6" t="n">
-        <v>59</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7">
@@ -550,10 +551,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="D7" t="n">
-        <v>230</v>
+        <v>367</v>
       </c>
     </row>
     <row r="9">
@@ -568,211 +569,229 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Galatians 2</t>
+          <t>Galatians 10</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Richmond Annan</t>
+          <t>Nii Nkunim Armar</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Galatians 2 (Hold)</t>
+          <t>Galatians 2</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Edwin Ogoe</t>
+          <t>Richmond Annan</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Galatians 4</t>
+          <t>Galatians 2 (Hold)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Eric Boachie Yiadom</t>
+          <t>Edwin Ogoe</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Galatians 5</t>
+          <t>Galatians 4</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Michael Oteng</t>
+          <t>Eric Boachie Yiadom</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>103</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Galatians 8</t>
+          <t>Galatians 5</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Caleb Osei-Kofi</t>
+          <t>Michael Oteng</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="D14" t="n">
-        <v>85</v>
+        <v>163</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Galatians 9</t>
+          <t>Galatians 8</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Divine Olubakinde</t>
+          <t>Caleb Osei-Kofi</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="D15" t="n">
-        <v>54</v>
+        <v>163</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>Galatians 9</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Divine Olubakinde</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>54</v>
+      </c>
+      <c r="D16" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>Galatians Total</t>
         </is>
       </c>
-      <c r="C16" t="n">
-        <v>515</v>
-      </c>
-      <c r="D16" t="n">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Galatians 3</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Joseph Teye</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>79</v>
-      </c>
-      <c r="D18" t="n">
-        <v>64</v>
+      <c r="C17" t="n">
+        <v>421</v>
+      </c>
+      <c r="D17" t="n">
+        <v>751</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Galatians 6 A</t>
+          <t>Galatians 3</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nana Kofi Danso-Mensah</t>
+          <t>Joseph Teye</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>99</v>
+        <v>64</v>
       </c>
       <c r="D19" t="n">
-        <v>164</v>
+        <v>211</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Galatians 7</t>
+          <t>Galatians 6 A</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Albert Gillies Heward-Mills</t>
+          <t>Nana Kofi Danso-Mensah</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>144</v>
+        <v>164</v>
       </c>
       <c r="D20" t="n">
-        <v>150</v>
+        <v>308</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>Galatians 7</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Albert Gillies Heward-Mills</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>150</v>
+      </c>
+      <c r="D21" t="n">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>Jesus Night Total</t>
         </is>
       </c>
-      <c r="C21" t="n">
-        <v>322</v>
-      </c>
-      <c r="D21" t="n">
+      <c r="C22" t="n">
         <v>378</v>
       </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="D22" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="C23" t="n">
-        <v>1069</v>
-      </c>
-      <c r="D23" t="n">
-        <v>1006</v>
+      <c r="C24" t="n">
+        <v>1035</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2022</v>
       </c>
     </row>
   </sheetData>
@@ -786,7 +805,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -802,152 +821,26 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>28/06</t>
+          <t>05/07</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>05/07</t>
+          <t>12/07</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Campus Anagkazo</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Nayram Gblorkpor</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Limann</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Kwesi Boadu-Amoama</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Mensah Sarbah Poimen</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Prince Okai</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>20</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Prince of Peace New</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Joseph Akyem</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Revelations</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Edna Adorshie</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>3</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Sarbah</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Joseph Teye</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>33</v>
-      </c>
-      <c r="D7" t="n">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Sey</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Dennis Kpogli</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>18</v>
-      </c>
-      <c r="D8" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>79</v>
-      </c>
-      <c r="D9" t="n">
-        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -961,7 +854,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -977,28 +870,28 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>28/06</t>
+          <t>05/07</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>05/07</t>
+          <t>12/07</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>UPSA Campus Hostels</t>
+          <t>Campus Anagkazo</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Andrew Heward-Mills</t>
+          <t>Nayram Gblorkpor</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>17</v>
@@ -1007,86 +900,122 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Upsa Diaspora</t>
+          <t>Limann</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bright Nurtey Tettey Tetteh</t>
+          <t>Kwesi Boadu-Amoama</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>UPSA Green Hostel</t>
+          <t>Mensah Sarbah Poimen</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Desmond Hlorgbey</t>
+          <t>Prince Okai</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>UPSA Hostels A &amp; B</t>
+          <t>Prince of Peace New</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Jayson Quarshie</t>
+          <t>Joseph Akyem</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>28</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>UPSA Rawlings Hostel</t>
+          <t>Revelations</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Eric Boachie Yiadom</t>
+          <t>Edna Adorshie</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Sarbah</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Joseph Teye</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>34</v>
+      </c>
+      <c r="D7" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Sey</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Dennis Kpogli</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>17</v>
+      </c>
+      <c r="D8" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>80</v>
-      </c>
-      <c r="D7" t="n">
-        <v>70</v>
+      <c r="C9" t="n">
+        <v>64</v>
+      </c>
+      <c r="D9" t="n">
+        <v>211</v>
       </c>
     </row>
   </sheetData>
@@ -1100,7 +1029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1116,224 +1045,98 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>28/06</t>
+          <t>05/07</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>05/07</t>
+          <t>12/07</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AIT</t>
+          <t>UPSA Campus Hostels</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Lawrence Adetunji</t>
+          <t>Andrew Heward-Mills</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AIT Yeshua</t>
+          <t>Upsa Diaspora</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Jonathan Ekhagbai</t>
+          <t>Bright Nurtey Tettey Tetteh</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Aparche</t>
+          <t>UPSA Green Hostel</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cyrus-Dag Stephens</t>
+          <t>Desmond Hlorgbey</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Encephal College of Health</t>
+          <t>UPSA Hostels A &amp; B</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Samuel Tigah</t>
+          <t>Jayson Quarshie</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Galilea</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Lady Vanessa Osei</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="D6" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>GTUC</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Richard Manu</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>8</v>
-      </c>
-      <c r="D7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>GTUC Allos</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Michael Oteng</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>GTUC Allos 3</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Sylvester Ntumy</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>12</v>
-      </c>
-      <c r="D9" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>GTUC Main Campus</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Jeremiah Ashong</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>36</v>
-      </c>
-      <c r="D10" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Kings/Regent</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Prince Forson</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>12</v>
-      </c>
-      <c r="D11" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Korle Bu Light</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Sonia Elolo</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>10</v>
-      </c>
-      <c r="D12" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>116</v>
-      </c>
-      <c r="D13" t="n">
-        <v>97</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -1347,7 +1150,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1363,296 +1166,224 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>28/06</t>
+          <t>05/07</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>05/07</t>
+          <t>12/07</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Akuafo New</t>
+          <t>AIT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Karyn Tagoe</t>
+          <t>Lawrence Adetunji</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bani</t>
+          <t>AIT Yeshua</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kojo Afriyie</t>
+          <t>Jonathan Ekhagbai</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Block A Annex</t>
+          <t>Aparche</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Marcia Adomako</t>
+          <t>Cyrus-Dag Stephens</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Block B Annex New</t>
+          <t>Encephal College of Health</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kevin Brown</t>
+          <t>Samuel Tigah</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Commonwealth</t>
+          <t>Galilea</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Peter Tefuttor</t>
+          <t>Lady Vanessa Osei</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Diamond Jubilee</t>
+          <t>GTUC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Emelda Antwi-Agyei</t>
+          <t>Richard Manu</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Evandy</t>
+          <t>GTUC Allos</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Delali Apedu</t>
+          <t>Michael Oteng</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Evandy Annex New</t>
+          <t>GTUC Allos 3</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Caroline Hammond</t>
+          <t>Sylvester Ntumy</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Pent B</t>
+          <t>GTUC Main Campus</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Yves Mensah</t>
+          <t>Jeremiah Ashong</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D10" t="n">
-        <v>14</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Pent C</t>
+          <t>Kings/Regent</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Roland Cudjoe</t>
+          <t>Prince Forson</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D11" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Pent Old &amp; A</t>
+          <t>Korle Bu Light</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Nana Kofi Danso-Mensah</t>
+          <t>Sonia Elolo</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D12" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TF</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Elizabeth Obeng Adu</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>97</v>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>TF Annex New</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Samuel Boateng</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Volta</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Stephanie Seglah</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>9</v>
-      </c>
-      <c r="D15" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Volta Annex New</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Esllah Osei</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>99</v>
-      </c>
-      <c r="D17" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>
@@ -1666,7 +1397,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1682,404 +1413,296 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>28/06</t>
+          <t>05/07</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>05/07</t>
+          <t>12/07</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Akuafo Charis</t>
+          <t>Akuafo New</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Stephen Asare Osei</t>
+          <t>Karyn Tagoe</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Akuafo Hall 1 New</t>
+          <t>Bani</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Fredrick Anokye</t>
+          <t>Kojo Afriyie</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Akuafo Hall 2 New</t>
+          <t>Block A Annex</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Dacosta Amponsah</t>
+          <t>Marcia Adomako</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Area 1  Logos</t>
+          <t>Block B Annex New</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Erasmus Laryea</t>
+          <t>Kevin Brown</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Commonwealth 1</t>
+          <t>Commonwealth</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Lois Osei</t>
+          <t>Peter Tefuttor</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Commonwealth 2 New</t>
+          <t>Diamond Jubilee</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>David Arhin</t>
+          <t>Emelda Antwi-Agyei</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Diamond Jubilee 1</t>
+          <t>Evandy</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Deborah Wiredu</t>
+          <t>Delali Apedu</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Diamond Jubilee 2</t>
+          <t>Evandy Annex New</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Abena Kyeremaa</t>
+          <t>Caroline Hammond</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Jesus Night TF New</t>
+          <t>Pent B</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Jochebed Lawson-Heymann</t>
+          <t>Yves Mensah</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Kwapong</t>
+          <t>Pent C</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Eunice Owusu</t>
+          <t>Roland Cudjoe</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Legon Hall</t>
+          <t>Pent Old &amp; A</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Edberg Ayensu</t>
+          <t>Nana Kofi Danso-Mensah</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Main Campus Allos</t>
+          <t>TF</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Albert Gillies Heward-Mills</t>
+          <t>Elizabeth Obeng Adu</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Main Campus Dunamis</t>
+          <t>TF Annex New</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nana Kwame Barima</t>
+          <t>Samuel Boateng</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Main Campus Hagios</t>
+          <t>Volta</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Philmorra Laryea Okorley</t>
+          <t>Stephanie Seglah</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Main Campus Parakletos</t>
+          <t>Volta Annex New</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Melissa Meledi</t>
+          <t>Esllah Osei</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Main Campus Pistis</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Richard Mawuli Sogbo</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>18</v>
+        <v>164</v>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Main Campus Proskuneo</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Isaac Baidoo</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>17</v>
-      </c>
-      <c r="D18" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Main Campus Tsalach</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Jennifer Aidoo</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>16</v>
-      </c>
-      <c r="D19" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Main campus Zogreo</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Elinam Fiagbe</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Sey New</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Frank Anokye</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Volta Hall</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Precious Antwi</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>144</v>
-      </c>
-      <c r="D23" t="n">
-        <v>150</v>
+        <v>308</v>
       </c>
     </row>
   </sheetData>
@@ -2093,7 +1716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2109,188 +1732,404 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>28/06</t>
+          <t>05/07</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>05/07</t>
+          <t>12/07</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AKUAFO</t>
+          <t>Akuafo Charis</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Foanor Alloh</t>
+          <t>Stephen Asare Osei</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Akuafo Hall 6</t>
+          <t>Akuafo Hall 1 New</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ruby Nelson</t>
+          <t>Fredrick Anokye</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Akuafo Zoe</t>
+          <t>Akuafo Hall 2 New</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Enoch Bentil</t>
+          <t>Dacosta Amponsah</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ELU</t>
+          <t>Area 1  Logos</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tracy Osei</t>
+          <t>Erasmus Laryea</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Legon hall</t>
+          <t>Commonwealth 1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nana Ahema Forson</t>
+          <t>Lois Osei</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Legon Hall B</t>
+          <t>Commonwealth 2 New</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Yosi Forson</t>
+          <t>David Arhin</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Volta</t>
+          <t>Diamond Jubilee 1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Caleb Osei-Kofi</t>
+          <t>Deborah Wiredu</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Volta Mega</t>
+          <t>Diamond Jubilee 2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Doris Ainooh</t>
+          <t>Abena Kyeremaa</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Volta Others</t>
+          <t>Jesus Night TF New</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Rachael Sekyiwaaa</t>
+          <t>Jochebed Lawson-Heymann</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>Kwapong</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Eunice Owusu</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>8</v>
+      </c>
+      <c r="D11" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Legon Hall</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Edberg Ayensu</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Main Campus Allos</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Albert Gillies Heward-Mills</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>62</v>
+      </c>
+      <c r="D13" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Main Campus Dunamis</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Nana Kwame Barima</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>7</v>
+      </c>
+      <c r="D14" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Main Campus Hagios</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Philmorra Laryea Okorley</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Main Campus Parakletos</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Melissa Meledi</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Main Campus Pistis</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Richard Mawuli Sogbo</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>16</v>
+      </c>
+      <c r="D17" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Main Campus Proskuneo</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Isaac Baidoo</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>7</v>
+      </c>
+      <c r="D18" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Main Campus Tsalach</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Jennifer Aidoo</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>15</v>
+      </c>
+      <c r="D19" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Main campus Zogreo</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Elinam Fiagbe</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Sey New</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Frank Anokye</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>4</v>
+      </c>
+      <c r="D21" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Volta Hall</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Precious Antwi</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C11" t="n">
-        <v>90</v>
-      </c>
-      <c r="D11" t="n">
-        <v>85</v>
+      <c r="C23" t="n">
+        <v>150</v>
+      </c>
+      <c r="D23" t="n">
+        <v>385</v>
       </c>
     </row>
   </sheetData>
@@ -2320,36 +2159,247 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>28/06</t>
+          <t>05/07</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>05/07</t>
+          <t>12/07</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>UPSA Allos 1</t>
+          <t>AKUAFO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Papa Kojo Amoakwa</t>
+          <t>Foanor Alloh</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>Akuafo Hall 6</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ruby Nelson</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Akuafo Zoe</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Enoch Bentil</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>16</v>
+      </c>
+      <c r="D4" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ELU</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Tracy Osei</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Legon hall</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Nana Ahema Forson</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>10</v>
+      </c>
+      <c r="D6" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Legon Hall B</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Yosi Forson</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>9</v>
+      </c>
+      <c r="D7" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Volta</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Caleb Osei-Kofi</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>31</v>
+      </c>
+      <c r="D8" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Volta Mega</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Doris Ainooh</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>10</v>
+      </c>
+      <c r="D9" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Volta Others</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Rachael Sekyiwaaa</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>85</v>
+      </c>
+      <c r="D11" t="n">
+        <v>163</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>05/07</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>12/07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>UPSA Allos 1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Papa Kojo Amoakwa</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>UPSA Allos 2</t>
         </is>
       </c>
@@ -2362,7 +2412,7 @@
         <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
@@ -2377,7 +2427,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -2413,10 +2463,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -2431,10 +2481,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
@@ -2449,10 +2499,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
@@ -2467,10 +2517,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10">
@@ -2498,10 +2548,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="D11" t="n">
-        <v>54</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -2531,12 +2581,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>28/06</t>
+          <t>05/07</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>05/07</t>
+          <t>12/07</t>
         </is>
       </c>
     </row>
@@ -2552,10 +2602,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D2" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
@@ -2570,10 +2620,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -2583,10 +2633,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="D4" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -2600,7 +2650,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2616,12 +2666,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>28/06</t>
+          <t>05/07</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>05/07</t>
+          <t>12/07</t>
         </is>
       </c>
     </row>
@@ -2691,10 +2741,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="D5" t="n">
-        <v>62</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6">
@@ -2709,7 +2759,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -2763,21 +2813,21 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D9" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Taifa Burkina</t>
+          <t>Kisseman</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Samuel Brown</t>
+          <t>Victoria Affran</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -2790,14 +2840,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>Taifa Burkina</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Samuel Brown</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C11" t="n">
-        <v>93</v>
-      </c>
-      <c r="D11" t="n">
+      <c r="C12" t="n">
         <v>85</v>
+      </c>
+      <c r="D12" t="n">
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -2827,12 +2895,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>28/06</t>
+          <t>05/07</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>05/07</t>
+          <t>12/07</t>
         </is>
       </c>
     </row>
@@ -2851,7 +2919,7 @@
         <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
@@ -2866,10 +2934,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
@@ -2887,7 +2955,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -2905,7 +2973,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -2920,10 +2988,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
@@ -2938,10 +3006,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
@@ -2956,10 +3024,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9">
@@ -2969,10 +3037,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D9" t="n">
-        <v>17</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -3002,12 +3070,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>28/06</t>
+          <t>05/07</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>05/07</t>
+          <t>12/07</t>
         </is>
       </c>
     </row>
@@ -3023,10 +3091,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3">
@@ -3041,10 +3109,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D3" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4">
@@ -3059,10 +3127,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
@@ -3072,10 +3140,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D5" t="n">
-        <v>48</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -3105,12 +3173,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>28/06</t>
+          <t>05/07</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>05/07</t>
+          <t>12/07</t>
         </is>
       </c>
     </row>
@@ -3144,10 +3212,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -3162,10 +3230,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D4" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
@@ -3180,10 +3248,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
@@ -3201,7 +3269,7 @@
         <v>11</v>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
@@ -3216,10 +3284,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
@@ -3229,10 +3297,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="D8" t="n">
-        <v>59</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -3262,12 +3330,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>28/06</t>
+          <t>05/07</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>05/07</t>
+          <t>12/07</t>
         </is>
       </c>
     </row>
@@ -3283,10 +3351,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -3301,10 +3369,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -3319,10 +3387,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -3332,10 +3400,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -3349,7 +3417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3365,224 +3433,26 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>28/06</t>
+          <t>05/07</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>05/07</t>
+          <t>12/07</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Accra City</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Ferdinand Adams</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Adabraka</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Prince Agbesi</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Arena</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Zephaniah Lartey</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>24</v>
-      </c>
-      <c r="D4" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Arena Allos</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Eric Akoto</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>ATU Church</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>James Pekyie</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>17</v>
-      </c>
-      <c r="D6" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>ATU Main Campus</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Racheal Boamah</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>13</v>
-      </c>
-      <c r="D7" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>City Campus</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Abednego Abbey</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>30</v>
-      </c>
-      <c r="D8" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Jamestown</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Joel Quartey</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>12</v>
-      </c>
-      <c r="D9" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Jamestown Allos</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Ishmael Oplerm</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>12</v>
-      </c>
-      <c r="D10" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>UssherFort</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Seth Kpelebe</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>10</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Yours and Ours</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Emmanuel Otiboe</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>10</v>
-      </c>
-      <c r="D12" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>136</v>
-      </c>
-      <c r="D13" t="n">
-        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -3596,7 +3466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3612,26 +3482,224 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>28/06</t>
+          <t>05/07</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>05/07</t>
+          <t>12/07</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>Accra City</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Ferdinand Adams</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Adabraka</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Prince Agbesi</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Arena</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Zephaniah Lartey</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>11</v>
+      </c>
+      <c r="D4" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Arena Allos</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Eric Akoto</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>19</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ATU Church</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>James Pekyie</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>11</v>
+      </c>
+      <c r="D6" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ATU Main Campus</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Racheal Boamah</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>17</v>
+      </c>
+      <c r="D7" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>City Campus</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Abednego Abbey</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>23</v>
+      </c>
+      <c r="D8" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Jamestown</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Joel Quartey</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>9</v>
+      </c>
+      <c r="D9" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Jamestown Allos</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ishmael Oplerm</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>UssherFort</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Seth Kpelebe</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Yours and Ours</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Emmanuel Otiboe</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>9</v>
+      </c>
+      <c r="D12" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
+      <c r="C13" t="n">
+        <v>104</v>
+      </c>
+      <c r="D13" t="n">
+        <v>202</v>
       </c>
     </row>
   </sheetData>

--- a/Sunday_Arrivals.xlsx
+++ b/Sunday_Arrivals.xlsx
@@ -16,14 +16,13 @@
     <sheet name="Galatians 1" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Galatians 10" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Galatians 2" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Galatians 2 (Hold)" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Galatians 3" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Galatians 4" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Galatians 5" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Galatians 6 A" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Galatians 7" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Galatians 8" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Galatians 9" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Galatians 3" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Galatians 4" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Galatians 5" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Galatians 6 A" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Galatians 7" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Galatians 8" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Galatians 9" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,12 +444,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>05/07</t>
+          <t>12/07</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>12/07</t>
+          <t>19/07</t>
         </is>
       </c>
     </row>
@@ -466,10 +465,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D2" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -484,10 +483,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="D3" t="n">
-        <v>97</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4">
@@ -502,10 +501,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>23</v>
+        <v>66</v>
       </c>
       <c r="D4" t="n">
-        <v>78</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5">
@@ -520,10 +519,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>48</v>
+        <v>81</v>
       </c>
       <c r="D5" t="n">
-        <v>81</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6">
@@ -538,10 +537,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="D6" t="n">
-        <v>82</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7">
@@ -551,10 +550,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>236</v>
+        <v>366</v>
       </c>
       <c r="D7" t="n">
-        <v>367</v>
+        <v>229</v>
       </c>
     </row>
     <row r="9">
@@ -569,10 +568,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -587,10 +586,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
@@ -605,193 +604,175 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>104</v>
+        <v>202</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>132</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Galatians 2 (Hold)</t>
+          <t>Galatians 4</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Edwin Ogoe</t>
+          <t>Eric Boachie Yiadom</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Galatians 4</t>
+          <t>Galatians 5</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Eric Boachie Yiadom</t>
+          <t>Michael Oteng</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>70</v>
+        <v>163</v>
       </c>
       <c r="D13" t="n">
-        <v>103</v>
+        <v>130</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Galatians 5</t>
+          <t>Galatians 8</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Michael Oteng</t>
+          <t>Caleb Osei-Kofi</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>97</v>
+        <v>174</v>
       </c>
       <c r="D14" t="n">
-        <v>163</v>
+        <v>85</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Galatians 8</t>
+          <t>Galatians 9</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Caleb Osei-Kofi</t>
+          <t>Divine Olubakinde</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="D15" t="n">
-        <v>163</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Galatians 9</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Divine Olubakinde</t>
+          <t>Galatians Total</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>54</v>
+        <v>762</v>
       </c>
       <c r="D16" t="n">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Galatians Total</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>421</v>
-      </c>
-      <c r="D17" t="n">
-        <v>751</v>
+        <v>498</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Galatians 3</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Joseph Teye</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>211</v>
+      </c>
+      <c r="D18" t="n">
+        <v>103</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Galatians 3</t>
+          <t>Galatians 6 A</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Joseph Teye</t>
+          <t>Nana Kofi Danso-Mensah</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>64</v>
+        <v>308</v>
       </c>
       <c r="D19" t="n">
-        <v>211</v>
+        <v>149</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Galatians 6 A</t>
+          <t>Galatians 7</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Nana Kofi Danso-Mensah</t>
+          <t>Albert Gillies Heward-Mills</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>164</v>
+        <v>385</v>
       </c>
       <c r="D20" t="n">
-        <v>308</v>
+        <v>172</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Galatians 7</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Albert Gillies Heward-Mills</t>
+          <t>Jesus Night Total</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>150</v>
+        <v>904</v>
       </c>
       <c r="D21" t="n">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Jesus Night Total</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>378</v>
-      </c>
-      <c r="D22" t="n">
-        <v>904</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="C24" t="n">
-        <v>1035</v>
-      </c>
-      <c r="D24" t="n">
-        <v>2022</v>
+      <c r="C23" t="n">
+        <v>2032</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1151</v>
       </c>
     </row>
   </sheetData>
@@ -805,7 +786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -821,26 +802,152 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>05/07</t>
+          <t>12/07</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>12/07</t>
+          <t>19/07</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>Campus Anagkazo</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Nayram Gblorkpor</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>17</v>
+      </c>
+      <c r="D2" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Limann</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kwesi Boadu-Amoama</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>11</v>
+      </c>
+      <c r="D3" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Mensah Sarbah Poimen</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Prince Okai</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>34</v>
+      </c>
+      <c r="D4" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Prince of Peace New</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Joseph Akyem</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>47</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Revelations</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Edna Adorshie</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>10</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Sarbah</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Joseph Teye</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>52</v>
+      </c>
+      <c r="D7" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Sey</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Dennis Kpogli</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>40</v>
+      </c>
+      <c r="D8" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
+      <c r="C9" t="n">
+        <v>211</v>
+      </c>
+      <c r="D9" t="n">
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -854,7 +961,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -870,152 +977,98 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>05/07</t>
+          <t>12/07</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>12/07</t>
+          <t>19/07</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Campus Anagkazo</t>
+          <t>UPSA Campus Hostels</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Nayram Gblorkpor</t>
+          <t>Andrew Heward-Mills</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="D2" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Limann</t>
+          <t>Upsa Diaspora</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kwesi Boadu-Amoama</t>
+          <t>Bright Nurtey Tettey Tetteh</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Mensah Sarbah Poimen</t>
+          <t>UPSA Green Hostel</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Prince Okai</t>
+          <t>Desmond Hlorgbey</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Prince of Peace New</t>
+          <t>UPSA Hostels A &amp; B</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Joseph Akyem</t>
+          <t>Jayson Quarshie</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="D5" t="n">
-        <v>47</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Revelations</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Edna Adorshie</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>103</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Sarbah</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Joseph Teye</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>34</v>
-      </c>
-      <c r="D7" t="n">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Sey</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Dennis Kpogli</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>17</v>
-      </c>
-      <c r="D8" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>64</v>
-      </c>
-      <c r="D9" t="n">
-        <v>211</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -1029,7 +1082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1045,42 +1098,42 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>05/07</t>
+          <t>12/07</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>12/07</t>
+          <t>19/07</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>UPSA Campus Hostels</t>
+          <t>AIT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Andrew Heward-Mills</t>
+          <t>Lawrence Adetunji</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Upsa Diaspora</t>
+          <t>AIT Yeshua</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bright Nurtey Tettey Tetteh</t>
+          <t>Jonathan Ekhagbai</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -1093,50 +1146,176 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>UPSA Green Hostel</t>
+          <t>Aparche</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Desmond Hlorgbey</t>
+          <t>Cyrus-Dag Stephens</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D4" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>UPSA Hostels A &amp; B</t>
+          <t>Encephal College of Health</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Jayson Quarshie</t>
+          <t>Samuel Tigah</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Galilea</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Lady Vanessa Osei</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>33</v>
+      </c>
+      <c r="D6" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>GTUC</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Richard Manu</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>12</v>
+      </c>
+      <c r="D7" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>GTUC Allos</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Michael Oteng</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>GTUC Allos 3</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Sylvester Ntumy</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>10</v>
+      </c>
+      <c r="D9" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>GTUC Main Campus</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Jeremiah Ashong</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>43</v>
+      </c>
+      <c r="D10" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Kings/Regent</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Prince Forson</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>23</v>
+      </c>
+      <c r="D11" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Korle Bu Light</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Sonia Elolo</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>16</v>
+      </c>
+      <c r="D12" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>70</v>
-      </c>
-      <c r="D6" t="n">
-        <v>103</v>
+      <c r="C13" t="n">
+        <v>163</v>
+      </c>
+      <c r="D13" t="n">
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -1150,7 +1329,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1166,28 +1345,28 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>05/07</t>
+          <t>12/07</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>12/07</t>
+          <t>19/07</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AIT</t>
+          <t>Akuafo New</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Lawrence Adetunji</t>
+          <t>Karyn Tagoe</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D2" t="n">
         <v>8</v>
@@ -1196,178 +1375,178 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AIT Yeshua</t>
+          <t>Area 1 Royals</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Jonathan Ekhagbai</t>
+          <t>Kwame Darteh</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Aparche</t>
+          <t>Bani</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cyrus-Dag Stephens</t>
+          <t>Kojo Afriyie</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Encephal College of Health</t>
+          <t>Block A Annex</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Samuel Tigah</t>
+          <t>Marcia Adomako</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Galilea</t>
+          <t>Block B Annex New</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Lady Vanessa Osei</t>
+          <t>Kevin Brown</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D6" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GTUC</t>
+          <t>Commonwealth</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Richard Manu</t>
+          <t>Peter Tefuttor</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GTUC Allos</t>
+          <t>Diamond Jubilee</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Michael Oteng</t>
+          <t>Emelda Antwi-Agyei</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GTUC Allos 3</t>
+          <t>Evandy</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Sylvester Ntumy</t>
+          <t>Delali Apedu</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GTUC Main Campus</t>
+          <t>Evandy Annex New</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Jeremiah Ashong</t>
+          <t>Caroline Hammond</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>43</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Kings/Regent</t>
+          <t>Pent B</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Prince Forson</t>
+          <t>Yves Mensah</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="D11" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Korle Bu Light</t>
+          <t>Pent C</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sonia Elolo</t>
+          <t>Roland Cudjoe</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D12" t="n">
         <v>16</v>
@@ -1376,14 +1555,86 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>Pent Old &amp; A</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Nana Kofi Danso-Mensah</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>31</v>
+      </c>
+      <c r="D13" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TF Annex New</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Samuel Boateng</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>19</v>
+      </c>
+      <c r="D14" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Volta</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Stephanie Seglah</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>25</v>
+      </c>
+      <c r="D15" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Volta Annex New</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Esllah Osei</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>20</v>
+      </c>
+      <c r="D16" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C13" t="n">
-        <v>97</v>
-      </c>
-      <c r="D13" t="n">
-        <v>163</v>
+      <c r="C17" t="n">
+        <v>308</v>
+      </c>
+      <c r="D17" t="n">
+        <v>149</v>
       </c>
     </row>
   </sheetData>
@@ -1397,7 +1648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1413,296 +1664,404 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>05/07</t>
+          <t>12/07</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>12/07</t>
+          <t>19/07</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Akuafo New</t>
+          <t>Akuafo Charis</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Karyn Tagoe</t>
+          <t>Stephen Asare Osei</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bani</t>
+          <t>Akuafo Hall 1 New</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kojo Afriyie</t>
+          <t>Fredrick Anokye</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Block A Annex</t>
+          <t>Akuafo Hall 2 New</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Marcia Adomako</t>
+          <t>Dacosta Amponsah</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Block B Annex New</t>
+          <t>Area 1  Logos</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kevin Brown</t>
+          <t>Erasmus Laryea</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D5" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Commonwealth</t>
+          <t>Commonwealth 1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Peter Tefuttor</t>
+          <t>Lois Osei</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D6" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Diamond Jubilee</t>
+          <t>Commonwealth 2 New</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Emelda Antwi-Agyei</t>
+          <t>David Arhin</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Evandy</t>
+          <t>Diamond Jubilee 1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Delali Apedu</t>
+          <t>Deborah Wiredu</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D8" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Evandy Annex New</t>
+          <t>Diamond Jubilee 2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Caroline Hammond</t>
+          <t>Abena Kyeremaa</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Pent B</t>
+          <t>Jesus Night TF New</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Yves Mensah</t>
+          <t>Jochebed Lawson-Heymann</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Pent C</t>
+          <t>Kwapong</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Roland Cudjoe</t>
+          <t>Eunice Owusu</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D11" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Pent Old &amp; A</t>
+          <t>Legon Hall</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Nana Kofi Danso-Mensah</t>
+          <t>Edberg Ayensu</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TF</t>
+          <t>Main Campus Allos</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Elizabeth Obeng Adu</t>
+          <t>Albert Gillies Heward-Mills</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TF Annex New</t>
+          <t>Main Campus Dunamis</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Samuel Boateng</t>
+          <t>Nana Kwame Barima</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D14" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Volta</t>
+          <t>Main Campus Hagios</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Stephanie Seglah</t>
+          <t>Philmorra Laryea Okorley</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D15" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Volta Annex New</t>
+          <t>Main Campus Parakletos</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Esllah Osei</t>
+          <t>Melissa Meledi</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>Main Campus Pistis</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Richard Mawuli Sogbo</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>31</v>
+      </c>
+      <c r="D17" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Main Campus Proskuneo</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Isaac Baidoo</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>22</v>
+      </c>
+      <c r="D18" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Main Campus Tsalach</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Jennifer Aidoo</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>26</v>
+      </c>
+      <c r="D19" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Main campus Zogreo</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Elinam Fiagbe</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>17</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Sey New</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Frank Anokye</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>8</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Volta Hall</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Precious Antwi</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>20</v>
+      </c>
+      <c r="D22" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C17" t="n">
-        <v>164</v>
-      </c>
-      <c r="D17" t="n">
-        <v>308</v>
+      <c r="C23" t="n">
+        <v>385</v>
+      </c>
+      <c r="D23" t="n">
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -1716,7 +2075,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1732,82 +2091,82 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>05/07</t>
+          <t>12/07</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>12/07</t>
+          <t>19/07</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Akuafo Charis</t>
+          <t>AKUAFO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Stephen Asare Osei</t>
+          <t>Foanor Alloh</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Akuafo Hall 1 New</t>
+          <t>Akuafo Hall 6</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Fredrick Anokye</t>
+          <t>Ruby Nelson</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Akuafo Hall 2 New</t>
+          <t>Akuafo Zoe</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Dacosta Amponsah</t>
+          <t>Enoch Bentil</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Area 1  Logos</t>
+          <t>ELU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Erasmus Laryea</t>
+          <t>Tracy Osei</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D5" t="n">
         <v>14</v>
@@ -1816,320 +2175,104 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Commonwealth 1</t>
+          <t>Legon hall</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Lois Osei</t>
+          <t>Nana Ahema Forson</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Commonwealth 2 New</t>
+          <t>Legon Hall B</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>David Arhin</t>
+          <t>Yosi Forson</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Diamond Jubilee 1</t>
+          <t>Volta</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Deborah Wiredu</t>
+          <t>Caleb Osei-Kofi</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="D8" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Diamond Jubilee 2</t>
+          <t>Volta Mega</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Abena Kyeremaa</t>
+          <t>Doris Ainooh</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D9" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Jesus Night TF New</t>
+          <t>Volta Others</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Jochebed Lawson-Heymann</t>
+          <t>Rachael Sekyiwaaa</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Kwapong</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Eunice Owusu</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>8</v>
+        <v>174</v>
       </c>
       <c r="D11" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Legon Hall</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Edberg Ayensu</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Main Campus Allos</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Albert Gillies Heward-Mills</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>62</v>
-      </c>
-      <c r="D13" t="n">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Main Campus Dunamis</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Nana Kwame Barima</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>7</v>
-      </c>
-      <c r="D14" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Main Campus Hagios</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Philmorra Laryea Okorley</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Main Campus Parakletos</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Melissa Meledi</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>3</v>
-      </c>
-      <c r="D16" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Main Campus Pistis</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Richard Mawuli Sogbo</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>16</v>
-      </c>
-      <c r="D17" t="n">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Main Campus Proskuneo</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Isaac Baidoo</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>7</v>
-      </c>
-      <c r="D18" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Main Campus Tsalach</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Jennifer Aidoo</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>15</v>
-      </c>
-      <c r="D19" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Main campus Zogreo</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Elinam Fiagbe</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Sey New</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Frank Anokye</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>4</v>
-      </c>
-      <c r="D21" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Volta Hall</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Precious Antwi</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>150</v>
-      </c>
-      <c r="D23" t="n">
-        <v>385</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -2159,118 +2302,118 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>05/07</t>
+          <t>12/07</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>12/07</t>
+          <t>19/07</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AKUAFO</t>
+          <t>UMC Allos 1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Foanor Alloh</t>
+          <t>Papa Kojo Amoakwa</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Akuafo Hall 6</t>
+          <t>UMC Allos 2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ruby Nelson</t>
+          <t>Herbert Aidoo</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="D3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Akuafo Zoe</t>
+          <t>UMC Allos 3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Enoch Bentil</t>
+          <t>Jessica Adonu</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ELU</t>
+          <t>UMC Allos 4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tracy Osei</t>
+          <t>Linda Tunkum</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Legon hall</t>
+          <t>UMC Allos 5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nana Ahema Forson</t>
+          <t>Joshua Agymang</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Legon Hall B</t>
+          <t>UMC Allos 6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Yosi Forson</t>
+          <t>David Abuaku</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D7" t="n">
         <v>9</v>
@@ -2279,55 +2422,55 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Volta</t>
+          <t>UMC Allos 7</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Caleb Osei-Kofi</t>
+          <t>Blessing Umukoro</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>46</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Volta Mega</t>
+          <t>UMC Allos 8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Doris Ainooh</t>
+          <t>Divine Olubakinde</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="D9" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Volta Others</t>
+          <t>UMC Allos 9</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Rachael Sekyiwaaa</t>
+          <t>Chris Keelson</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -2337,221 +2480,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="D11" t="n">
-        <v>163</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Area</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Governor</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>05/07</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>12/07</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>UPSA Allos 1</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Papa Kojo Amoakwa</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>19</v>
-      </c>
-      <c r="D2" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>UPSA Allos 2</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Herbert Aidoo</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>11</v>
-      </c>
-      <c r="D3" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>UPSA Allos 3</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Marvellous Korsoku</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>UPSA Allos 4</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Linda Tunkum</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>UPSA Allos 5</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Joshua Agymang</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>3</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>UPSA Allos 6</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>David Abuaku</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>8</v>
-      </c>
-      <c r="D7" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>UPSA Allos 7</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Blessing Umukoro</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>8</v>
-      </c>
-      <c r="D8" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>UPSA Allos 8</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Divine Olubakinde</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>5</v>
-      </c>
-      <c r="D9" t="n">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>UPSA Allos 9</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Chris Keelson</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>54</v>
-      </c>
-      <c r="D11" t="n">
-        <v>102</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -2581,12 +2513,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>05/07</t>
+          <t>12/07</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>12/07</t>
+          <t>19/07</t>
         </is>
       </c>
     </row>
@@ -2598,14 +2530,14 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>David Yalleh</t>
+          <t>Richard Anku</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="D2" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -2620,7 +2552,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -2633,10 +2565,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D4" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -2666,12 +2598,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>05/07</t>
+          <t>12/07</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>12/07</t>
+          <t>19/07</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2640,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4">
@@ -2744,7 +2676,7 @@
         <v>62</v>
       </c>
       <c r="D5" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -2762,7 +2694,7 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
@@ -2798,7 +2730,7 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
@@ -2813,10 +2745,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="D9" t="n">
-        <v>46</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10">
@@ -2852,7 +2784,7 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -2862,10 +2794,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -2879,7 +2811,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2895,12 +2827,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>05/07</t>
+          <t>12/07</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>12/07</t>
+          <t>19/07</t>
         </is>
       </c>
     </row>
@@ -2916,10 +2848,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -2934,10 +2866,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -2952,7 +2884,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
         <v>2</v>
@@ -2970,77 +2902,59 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Haatso Palace</t>
+          <t>Haatso West</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Richard Anku</t>
+          <t>Michael Sarpong</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Haatso West</t>
+          <t>THS Westland</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Michael Sarpong</t>
+          <t>Joseph Halivor</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="D7" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>THS Westland</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Joseph Halivor</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>66</v>
       </c>
       <c r="D8" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>23</v>
-      </c>
-      <c r="D9" t="n">
-        <v>78</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -3070,12 +2984,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>05/07</t>
+          <t>12/07</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>12/07</t>
+          <t>19/07</t>
         </is>
       </c>
     </row>
@@ -3091,10 +3005,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="D2" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -3109,10 +3023,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D3" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4">
@@ -3127,10 +3041,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
@@ -3140,10 +3054,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>48</v>
+        <v>81</v>
       </c>
       <c r="D5" t="n">
-        <v>81</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -3173,12 +3087,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>05/07</t>
+          <t>12/07</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>12/07</t>
+          <t>19/07</t>
         </is>
       </c>
     </row>
@@ -3212,10 +3126,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D3" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -3230,10 +3144,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5">
@@ -3248,10 +3162,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D5" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6">
@@ -3266,10 +3180,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D6" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
@@ -3284,10 +3198,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -3297,10 +3211,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="D8" t="n">
-        <v>82</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -3314,7 +3228,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3330,80 +3244,26 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>05/07</t>
+          <t>12/07</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>12/07</t>
+          <t>19/07</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ACM</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Nii Nkunim Armar</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ACM 2</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Daniel Orleans-Lindsay</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ACM 3</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Joan Obakpolor</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>11</v>
-      </c>
-      <c r="D5" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3417,7 +3277,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3433,26 +3293,80 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>05/07</t>
+          <t>12/07</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>12/07</t>
+          <t>19/07</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>ACM</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Nii Nkunim Armar</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ACM 2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Daniel Orleans-Lindsay</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ACM 3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Joan Obakpolor</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D4" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
+      <c r="C5" t="n">
+        <v>18</v>
+      </c>
+      <c r="D5" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -3482,12 +3396,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>05/07</t>
+          <t>12/07</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>12/07</t>
+          <t>19/07</t>
         </is>
       </c>
     </row>
@@ -3503,7 +3417,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D2" t="n">
         <v>20</v>
@@ -3539,10 +3453,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D4" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -3557,7 +3471,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -3575,10 +3489,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D6" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
@@ -3593,10 +3507,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D7" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
@@ -3611,10 +3525,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D8" t="n">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9">
@@ -3629,10 +3543,10 @@
         </is>
       </c>
       <c r="C9" t="n">
+        <v>21</v>
+      </c>
+      <c r="D9" t="n">
         <v>9</v>
-      </c>
-      <c r="D9" t="n">
-        <v>21</v>
       </c>
     </row>
     <row r="10">
@@ -3647,10 +3561,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="D10" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11">
@@ -3665,10 +3579,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
@@ -3683,10 +3597,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">
@@ -3696,10 +3610,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>104</v>
+        <v>202</v>
       </c>
       <c r="D13" t="n">
-        <v>202</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>

--- a/Sunday_Arrivals.xlsx
+++ b/Sunday_Arrivals.xlsx
@@ -486,7 +486,7 @@
         <v>108</v>
       </c>
       <c r="D3" t="n">
-        <v>66</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4">
@@ -553,7 +553,7 @@
         <v>366</v>
       </c>
       <c r="D7" t="n">
-        <v>229</v>
+        <v>237</v>
       </c>
     </row>
     <row r="9">
@@ -772,7 +772,7 @@
         <v>2032</v>
       </c>
       <c r="D23" t="n">
-        <v>1151</v>
+        <v>1159</v>
       </c>
     </row>
   </sheetData>
@@ -2730,7 +2730,7 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9">
@@ -2797,7 +2797,7 @@
         <v>108</v>
       </c>
       <c r="D12" t="n">
-        <v>66</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/Sunday_Arrivals.xlsx
+++ b/Sunday_Arrivals.xlsx
@@ -444,12 +444,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>12/07</t>
+          <t>19/07</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>19/07</t>
+          <t>26/07</t>
         </is>
       </c>
     </row>
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="D2" t="n">
         <v>16</v>
@@ -483,10 +483,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="D3" t="n">
-        <v>74</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4">
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="D4" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5">
@@ -519,10 +519,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="D5" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6">
@@ -537,10 +537,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="D6" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>366</v>
+        <v>237</v>
       </c>
       <c r="D7" t="n">
-        <v>237</v>
+        <v>224</v>
       </c>
     </row>
     <row r="9">
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -604,10 +604,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>202</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -622,10 +622,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="D12" t="n">
-        <v>84</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13">
@@ -640,10 +640,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>163</v>
+        <v>130</v>
       </c>
       <c r="D13" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
     </row>
     <row r="14">
@@ -658,10 +658,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>174</v>
+        <v>85</v>
       </c>
       <c r="D14" t="n">
-        <v>85</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>102</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16">
@@ -689,10 +689,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>762</v>
+        <v>498</v>
       </c>
       <c r="D16" t="n">
-        <v>498</v>
+        <v>463</v>
       </c>
     </row>
     <row r="18">
@@ -707,10 +707,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>211</v>
+        <v>126</v>
       </c>
       <c r="D18" t="n">
-        <v>103</v>
+        <v>87</v>
       </c>
     </row>
     <row r="19">
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>308</v>
+        <v>141</v>
       </c>
       <c r="D19" t="n">
-        <v>149</v>
+        <v>116</v>
       </c>
     </row>
     <row r="20">
@@ -743,10 +743,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>385</v>
+        <v>149</v>
       </c>
       <c r="D20" t="n">
-        <v>172</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21">
@@ -756,10 +756,10 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>904</v>
+        <v>416</v>
       </c>
       <c r="D21" t="n">
-        <v>424</v>
+        <v>269</v>
       </c>
     </row>
     <row r="23">
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2032</v>
+        <v>1151</v>
       </c>
       <c r="D23" t="n">
-        <v>1159</v>
+        <v>956</v>
       </c>
     </row>
   </sheetData>
@@ -786,7 +786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -802,12 +802,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>12/07</t>
+          <t>19/07</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>19/07</t>
+          <t>26/07</t>
         </is>
       </c>
     </row>
@@ -823,131 +823,221 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Limann</t>
+          <t>Commonwealth 2 New</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kwesi Boadu-Amoama</t>
+          <t>David Arhin</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Mensah Sarbah Poimen</t>
+          <t>Diamond Jubilee 1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Prince Okai</t>
+          <t>Deborah Wiredu</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Prince of Peace New</t>
+          <t>Limann</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Joseph Akyem</t>
+          <t>Kwesi Boadu-Amoama</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>47</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Revelations</t>
+          <t>Main Campus Dunamis</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Edna Adorshie</t>
+          <t>Nana Kwame Barima</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sarbah</t>
+          <t>Main Campus Proskuneo</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Joseph Teye</t>
+          <t>Isaac Baidoo</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>52</v>
+        <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>39</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sey</t>
+          <t>Mensah Sarbah Poimen</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Dennis Kpogli</t>
+          <t>Prince Okai</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Prince of Peace New</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Joseph Akyem</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Revelations</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Edna Adorshie</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sarbah</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Joseph Teye</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>39</v>
+      </c>
+      <c r="D11" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Sey</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Dennis Kpogli</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>24</v>
+      </c>
+      <c r="D12" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Sey New</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Frank Anokye</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C9" t="n">
-        <v>211</v>
-      </c>
-      <c r="D9" t="n">
-        <v>103</v>
+      <c r="C14" t="n">
+        <v>126</v>
+      </c>
+      <c r="D14" t="n">
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -977,12 +1067,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>12/07</t>
+          <t>19/07</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>19/07</t>
+          <t>26/07</t>
         </is>
       </c>
     </row>
@@ -998,10 +1088,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="D2" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
@@ -1034,10 +1124,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D4" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5">
@@ -1052,10 +1142,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D5" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6">
@@ -1065,10 +1155,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="D6" t="n">
-        <v>84</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -1098,12 +1188,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>12/07</t>
+          <t>19/07</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>19/07</t>
+          <t>26/07</t>
         </is>
       </c>
     </row>
@@ -1119,10 +1209,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -1140,7 +1230,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -1155,7 +1245,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
         <v>8</v>
@@ -1173,10 +1263,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -1191,10 +1281,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D6" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7">
@@ -1209,10 +1299,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -1227,7 +1317,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -1245,10 +1335,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D9" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1263,7 +1353,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="D10" t="n">
         <v>30</v>
@@ -1281,10 +1371,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D11" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12">
@@ -1299,10 +1389,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
@@ -1312,10 +1402,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>163</v>
+        <v>130</v>
       </c>
       <c r="D13" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -1345,12 +1435,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>12/07</t>
+          <t>19/07</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>19/07</t>
+          <t>26/07</t>
         </is>
       </c>
     </row>
@@ -1366,10 +1456,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -1384,10 +1474,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -1402,10 +1492,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="D4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
@@ -1420,10 +1510,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
@@ -1438,7 +1528,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
         <v>6</v>
@@ -1456,16 +1546,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Diamond Jubilee</t>
+          <t>Diamond Jubilee New</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1474,10 +1564,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
@@ -1492,10 +1582,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D9" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
@@ -1510,10 +1600,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -1528,10 +1618,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D11" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
@@ -1546,10 +1636,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
@@ -1564,10 +1654,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="D13" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14">
@@ -1582,10 +1672,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -1600,10 +1690,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1618,10 +1708,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17">
@@ -1631,10 +1721,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>308</v>
+        <v>141</v>
       </c>
       <c r="D17" t="n">
-        <v>149</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -1648,7 +1738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1664,12 +1754,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>12/07</t>
+          <t>19/07</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>19/07</t>
+          <t>26/07</t>
         </is>
       </c>
     </row>
@@ -1703,10 +1793,10 @@
         </is>
       </c>
       <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
         <v>6</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -1721,10 +1811,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -1739,10 +1829,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -1757,311 +1847,221 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Commonwealth 2 New</t>
+          <t>Diamond Jubilee 2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>David Arhin</t>
+          <t>Abena Kyeremaa</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Diamond Jubilee 1</t>
+          <t>Jesus Night TF New</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Deborah Wiredu</t>
+          <t>Jochebed Lawson-Heymann</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Diamond Jubilee 2</t>
+          <t>Kwapong</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Abena Kyeremaa</t>
+          <t>Eunice Owusu</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Jesus Night TF New</t>
+          <t>Legon Hall</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Jochebed Lawson-Heymann</t>
+          <t>Edberg Ayensu</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Kwapong</t>
+          <t>Main Campus Allos</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Eunice Owusu</t>
+          <t>Albert Gillies Heward-Mills</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>12</v>
+        <v>83</v>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Legon Hall</t>
+          <t>Main Campus Hagios</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Edberg Ayensu</t>
+          <t>Philmorra Laryea Okorley</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Main Campus Allos</t>
+          <t>Main Campus Parakletos</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Albert Gillies Heward-Mills</t>
+          <t>Melissa Meledi</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>10</v>
       </c>
       <c r="D13" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Main Campus Dunamis</t>
+          <t>Main Campus Pistis</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nana Kwame Barima</t>
+          <t>Richard Mawuli Sogbo</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>20</v>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Main Campus Hagios</t>
+          <t>Main Campus Tsalach</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Philmorra Laryea Okorley</t>
+          <t>Jennifer Aidoo</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Main Campus Parakletos</t>
+          <t>Main campus Zogreo</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Melissa Meledi</t>
+          <t>Elinam Fiagbe</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Main Campus Pistis</t>
+          <t>Volta Hall</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Richard Mawuli Sogbo</t>
+          <t>Precious Antwi</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="D17" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Main Campus Proskuneo</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Isaac Baidoo</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>22</v>
+        <v>149</v>
       </c>
       <c r="D18" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Main Campus Tsalach</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Jennifer Aidoo</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>26</v>
-      </c>
-      <c r="D19" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Main campus Zogreo</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Elinam Fiagbe</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>17</v>
-      </c>
-      <c r="D20" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Sey New</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Frank Anokye</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>8</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Volta Hall</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Precious Antwi</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>20</v>
-      </c>
-      <c r="D22" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>385</v>
-      </c>
-      <c r="D23" t="n">
-        <v>172</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -2091,12 +2091,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>12/07</t>
+          <t>19/07</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>19/07</t>
+          <t>26/07</t>
         </is>
       </c>
     </row>
@@ -2112,10 +2112,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -2130,7 +2130,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -2151,7 +2151,7 @@
         <v>18</v>
       </c>
       <c r="D4" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
@@ -2166,10 +2166,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D5" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -2184,10 +2184,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
@@ -2202,10 +2202,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -2220,10 +2220,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="D8" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9">
@@ -2238,7 +2238,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
         <v>8</v>
@@ -2256,7 +2256,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
         <v>3</v>
@@ -2269,10 +2269,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>174</v>
+        <v>85</v>
       </c>
       <c r="D11" t="n">
-        <v>85</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -2302,12 +2302,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>12/07</t>
+          <t>19/07</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>19/07</t>
+          <t>26/07</t>
         </is>
       </c>
     </row>
@@ -2323,10 +2323,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -2341,10 +2341,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D3" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D8" t="n">
         <v>9</v>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
@@ -2480,10 +2480,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>102</v>
+        <v>60</v>
       </c>
       <c r="D11" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -2497,7 +2497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2513,12 +2513,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>12/07</t>
+          <t>19/07</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>19/07</t>
+          <t>26/07</t>
         </is>
       </c>
     </row>
@@ -2530,14 +2530,14 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Richard Anku</t>
+          <t>David Yalleh</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="D2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -2555,19 +2555,37 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Spintex Palace</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Richard Anku</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>29</v>
-      </c>
-      <c r="D4" t="n">
+      <c r="C5" t="n">
+        <v>16</v>
+      </c>
+      <c r="D5" t="n">
         <v>16</v>
       </c>
     </row>
@@ -2598,12 +2616,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>12/07</t>
+          <t>19/07</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>19/07</t>
+          <t>26/07</t>
         </is>
       </c>
     </row>
@@ -2637,10 +2655,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D3" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
@@ -2673,7 +2691,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -2691,7 +2709,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
         <v>9</v>
@@ -2727,10 +2745,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="D8" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
@@ -2745,10 +2763,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="D9" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
@@ -2766,7 +2784,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
@@ -2781,10 +2799,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -2794,10 +2812,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="D12" t="n">
-        <v>74</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -2827,12 +2845,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>12/07</t>
+          <t>19/07</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>19/07</t>
+          <t>26/07</t>
         </is>
       </c>
     </row>
@@ -2848,10 +2866,10 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>11</v>
+      </c>
+      <c r="D2" t="n">
         <v>12</v>
-      </c>
-      <c r="D2" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -2866,10 +2884,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -2887,7 +2905,7 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -2902,7 +2920,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -2920,10 +2938,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
@@ -2938,10 +2956,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -2951,10 +2969,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="D8" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -2984,12 +3002,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>12/07</t>
+          <t>19/07</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>19/07</t>
+          <t>26/07</t>
         </is>
       </c>
     </row>
@@ -3005,10 +3023,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D2" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
@@ -3023,10 +3041,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D3" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4">
@@ -3041,10 +3059,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
@@ -3054,10 +3072,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="D5" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -3087,12 +3105,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>12/07</t>
+          <t>19/07</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>19/07</t>
+          <t>26/07</t>
         </is>
       </c>
     </row>
@@ -3126,10 +3144,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -3144,10 +3162,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D4" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
@@ -3162,10 +3180,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D5" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -3180,10 +3198,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
@@ -3198,10 +3216,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -3211,10 +3229,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="D8" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -3244,12 +3262,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>12/07</t>
+          <t>19/07</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>19/07</t>
+          <t>26/07</t>
         </is>
       </c>
     </row>
@@ -3293,12 +3311,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>12/07</t>
+          <t>19/07</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>19/07</t>
+          <t>26/07</t>
         </is>
       </c>
     </row>
@@ -3314,7 +3332,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -3332,7 +3350,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -3353,7 +3371,7 @@
         <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -3363,10 +3381,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -3396,12 +3414,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>12/07</t>
+          <t>19/07</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>19/07</t>
+          <t>26/07</t>
         </is>
       </c>
     </row>
@@ -3420,7 +3438,7 @@
         <v>20</v>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -3453,10 +3471,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
@@ -3489,10 +3507,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D6" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7">
@@ -3507,10 +3525,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D7" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
@@ -3525,10 +3543,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="D8" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9">
@@ -3543,10 +3561,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
@@ -3561,10 +3579,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -3579,7 +3597,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D11" t="n">
         <v>10</v>
@@ -3597,10 +3615,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D12" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
@@ -3610,10 +3628,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>202</v>
+        <v>132</v>
       </c>
       <c r="D13" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>

--- a/Sunday_Arrivals.xlsx
+++ b/Sunday_Arrivals.xlsx
@@ -444,12 +444,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>19/07</t>
+          <t>26/07</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>26/07</t>
+          <t>02/08</t>
         </is>
       </c>
     </row>
@@ -468,7 +468,7 @@
         <v>16</v>
       </c>
       <c r="D2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -483,10 +483,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="D3" t="n">
-        <v>59</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4">
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D4" t="n">
-        <v>36</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5">
@@ -519,10 +519,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D5" t="n">
-        <v>67</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6">
@@ -537,10 +537,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D6" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>237</v>
+        <v>224</v>
       </c>
       <c r="D7" t="n">
-        <v>224</v>
+        <v>209</v>
       </c>
     </row>
     <row r="9">
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11">
@@ -604,10 +604,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>124</v>
       </c>
     </row>
     <row r="12">
@@ -622,10 +622,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="D12" t="n">
-        <v>73</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13">
@@ -640,10 +640,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="D13" t="n">
-        <v>110</v>
+        <v>104</v>
       </c>
     </row>
     <row r="14">
@@ -658,10 +658,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="D14" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>66</v>
+        <v>52</v>
       </c>
     </row>
     <row r="16">
@@ -689,10 +689,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>498</v>
+        <v>463</v>
       </c>
       <c r="D16" t="n">
-        <v>463</v>
+        <v>422</v>
       </c>
     </row>
     <row r="18">
@@ -707,10 +707,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>126</v>
+        <v>87</v>
       </c>
       <c r="D18" t="n">
-        <v>87</v>
+        <v>109</v>
       </c>
     </row>
     <row r="19">
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>141</v>
+        <v>116</v>
       </c>
       <c r="D19" t="n">
-        <v>116</v>
+        <v>137</v>
       </c>
     </row>
     <row r="20">
@@ -743,10 +743,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>149</v>
+        <v>66</v>
       </c>
       <c r="D20" t="n">
-        <v>66</v>
+        <v>97</v>
       </c>
     </row>
     <row r="21">
@@ -756,10 +756,10 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>416</v>
+        <v>269</v>
       </c>
       <c r="D21" t="n">
-        <v>269</v>
+        <v>343</v>
       </c>
     </row>
     <row r="23">
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1151</v>
+        <v>956</v>
       </c>
       <c r="D23" t="n">
-        <v>956</v>
+        <v>974</v>
       </c>
     </row>
   </sheetData>
@@ -802,12 +802,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>19/07</t>
+          <t>26/07</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>26/07</t>
+          <t>02/08</t>
         </is>
       </c>
     </row>
@@ -823,10 +823,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
@@ -877,10 +877,10 @@
         </is>
       </c>
       <c r="C5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D5" t="n">
         <v>9</v>
-      </c>
-      <c r="D5" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -898,7 +898,7 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -913,10 +913,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D8" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9">
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
@@ -967,10 +967,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -985,10 +985,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
@@ -1003,10 +1003,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D12" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13">
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -1034,10 +1034,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>126</v>
+        <v>87</v>
       </c>
       <c r="D14" t="n">
-        <v>87</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>19/07</t>
+          <t>26/07</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>26/07</t>
+          <t>02/08</t>
         </is>
       </c>
     </row>
@@ -1088,7 +1088,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D2" t="n">
         <v>22</v>
@@ -1124,10 +1124,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D4" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D5" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6">
@@ -1155,10 +1155,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="D6" t="n">
-        <v>73</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>19/07</t>
+          <t>26/07</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>26/07</t>
+          <t>02/08</t>
         </is>
       </c>
     </row>
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -1227,7 +1227,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
         <v>4</v>
@@ -1248,7 +1248,7 @@
         <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -1263,10 +1263,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
@@ -1281,10 +1281,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D6" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7">
@@ -1299,10 +1299,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -1335,10 +1335,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
@@ -1356,7 +1356,7 @@
         <v>30</v>
       </c>
       <c r="D10" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11">
@@ -1371,10 +1371,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12">
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13">
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="D13" t="n">
-        <v>110</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -1435,12 +1435,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>19/07</t>
+          <t>26/07</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>26/07</t>
+          <t>02/08</t>
         </is>
       </c>
     </row>
@@ -1456,10 +1456,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
@@ -1474,10 +1474,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="C5" t="n">
+        <v>11</v>
+      </c>
+      <c r="D5" t="n">
         <v>12</v>
-      </c>
-      <c r="D5" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="6">
@@ -1531,7 +1531,7 @@
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
@@ -1546,10 +1546,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -1564,10 +1564,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -1582,10 +1582,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
@@ -1600,10 +1600,10 @@
         </is>
       </c>
       <c r="C10" t="n">
+        <v>6</v>
+      </c>
+      <c r="D10" t="n">
         <v>4</v>
-      </c>
-      <c r="D10" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -1618,10 +1618,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12">
@@ -1636,10 +1636,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
@@ -1654,10 +1654,10 @@
         </is>
       </c>
       <c r="C13" t="n">
+        <v>11</v>
+      </c>
+      <c r="D13" t="n">
         <v>14</v>
-      </c>
-      <c r="D13" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="14">
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
         <v>3</v>
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -1708,10 +1708,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D16" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
@@ -1721,10 +1721,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>141</v>
+        <v>116</v>
       </c>
       <c r="D17" t="n">
-        <v>116</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>19/07</t>
+          <t>26/07</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>26/07</t>
+          <t>02/08</t>
         </is>
       </c>
     </row>
@@ -1793,10 +1793,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -1829,10 +1829,10 @@
         </is>
       </c>
       <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
         <v>5</v>
-      </c>
-      <c r="D5" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -1847,10 +1847,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1865,10 +1865,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1901,10 +1901,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1919,10 +1919,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1937,10 +1937,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>83</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12">
@@ -1958,7 +1958,7 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -1973,10 +1973,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14">
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D14" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15">
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D16" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17">
@@ -2045,10 +2045,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18">
@@ -2058,10 +2058,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>149</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
-        <v>66</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -2091,12 +2091,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>19/07</t>
+          <t>26/07</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>26/07</t>
+          <t>02/08</t>
         </is>
       </c>
     </row>
@@ -2112,10 +2112,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -2148,7 +2148,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
         <v>12</v>
@@ -2166,7 +2166,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
         <v>8</v>
@@ -2184,10 +2184,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
@@ -2202,10 +2202,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -2220,7 +2220,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D8" t="n">
         <v>25</v>
@@ -2259,7 +2259,7 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -2269,10 +2269,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="D11" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -2302,12 +2302,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>19/07</t>
+          <t>26/07</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>26/07</t>
+          <t>02/08</t>
         </is>
       </c>
     </row>
@@ -2323,10 +2323,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -2341,10 +2341,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -2359,7 +2359,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D4" t="n">
         <v>14</v>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -2434,7 +2434,7 @@
         <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D9" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -2480,10 +2480,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="D11" t="n">
-        <v>66</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -2513,12 +2513,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>19/07</t>
+          <t>26/07</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>26/07</t>
+          <t>02/08</t>
         </is>
       </c>
     </row>
@@ -2534,10 +2534,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -2552,10 +2552,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -2570,10 +2570,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -2586,7 +2586,7 @@
         <v>16</v>
       </c>
       <c r="D5" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -2616,12 +2616,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>19/07</t>
+          <t>26/07</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>26/07</t>
+          <t>02/08</t>
         </is>
       </c>
     </row>
@@ -2655,7 +2655,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D3" t="n">
         <v>21</v>
@@ -2694,7 +2694,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -2712,7 +2712,7 @@
         <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
@@ -2745,10 +2745,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9">
@@ -2763,10 +2763,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
@@ -2781,10 +2781,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
@@ -2799,7 +2799,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -2812,10 +2812,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="D12" t="n">
-        <v>59</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -2845,12 +2845,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>19/07</t>
+          <t>26/07</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>26/07</t>
+          <t>02/08</t>
         </is>
       </c>
     </row>
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3">
@@ -2884,10 +2884,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -2902,7 +2902,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -2938,10 +2938,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
@@ -2956,10 +2956,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D8" t="n">
-        <v>36</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>19/07</t>
+          <t>26/07</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>26/07</t>
+          <t>02/08</t>
         </is>
       </c>
     </row>
@@ -3023,10 +3023,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D2" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -3041,10 +3041,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D3" t="n">
-        <v>33</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
@@ -3059,10 +3059,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
@@ -3072,10 +3072,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D5" t="n">
-        <v>67</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -3105,12 +3105,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>19/07</t>
+          <t>26/07</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>26/07</t>
+          <t>02/08</t>
         </is>
       </c>
     </row>
@@ -3144,10 +3144,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -3162,10 +3162,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5">
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -3198,10 +3198,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -3216,10 +3216,10 @@
         </is>
       </c>
       <c r="C7" t="n">
+        <v>7</v>
+      </c>
+      <c r="D7" t="n">
         <v>8</v>
-      </c>
-      <c r="D7" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D8" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -3262,12 +3262,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>19/07</t>
+          <t>26/07</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>26/07</t>
+          <t>02/08</t>
         </is>
       </c>
     </row>
@@ -3311,12 +3311,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>19/07</t>
+          <t>26/07</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>26/07</t>
+          <t>02/08</t>
         </is>
       </c>
     </row>
@@ -3368,10 +3368,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5">
@@ -3381,10 +3381,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -3398,7 +3398,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>19/07</t>
+          <t>26/07</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>26/07</t>
+          <t>02/08</t>
         </is>
       </c>
     </row>
@@ -3435,10 +3435,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Prince Agbesi</t>
+          <t>Emmanuel Otiboe</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -3471,167 +3471,149 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Arena Allos</t>
+          <t>ATU Church</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Eric Akoto</t>
+          <t>James Pekyie</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ATU Church</t>
+          <t>ATU Main Campus</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>James Pekyie</t>
+          <t>Racheal Boamah</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ATU Main Campus</t>
+          <t>City Campus</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Racheal Boamah</t>
+          <t>Abednego Abbey</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>City Campus</t>
+          <t>Jamestown</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Abednego Abbey</t>
+          <t>Joel Quartey</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="D8" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Jamestown</t>
+          <t>Jamestown Allos</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Joel Quartey</t>
+          <t>Ishmael Oplerm</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Jamestown Allos</t>
+          <t>UssherFort</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ishmael Oplerm</t>
+          <t>Seth Kpelebe</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>UssherFort</t>
+          <t>Yours and Ours</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Seth Kpelebe</t>
+          <t>Prince Odum</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>10</v>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Yours and Ours</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Emmanuel Otiboe</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>14</v>
+        <v>136</v>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>132</v>
-      </c>
-      <c r="D13" t="n">
-        <v>136</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>

--- a/Sunday_Arrivals.xlsx
+++ b/Sunday_Arrivals.xlsx
@@ -444,12 +444,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>26/07</t>
+          <t>02/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>02/08</t>
+          <t>09/08</t>
         </is>
       </c>
     </row>
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -483,10 +483,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="D3" t="n">
-        <v>82</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4">
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="D4" t="n">
-        <v>53</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5">
@@ -519,10 +519,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="D5" t="n">
-        <v>18</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6">
@@ -537,10 +537,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D6" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="D7" t="n">
-        <v>209</v>
+        <v>213</v>
       </c>
     </row>
     <row r="9">
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D10" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -604,10 +604,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="D11" t="n">
-        <v>124</v>
+        <v>131</v>
       </c>
     </row>
     <row r="12">
@@ -622,10 +622,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="D12" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13">
@@ -640,10 +640,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="D13" t="n">
-        <v>104</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14">
@@ -658,10 +658,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D14" t="n">
-        <v>74</v>
+        <v>116</v>
       </c>
     </row>
     <row r="15">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="D15" t="n">
-        <v>52</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16">
@@ -689,10 +689,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>463</v>
+        <v>422</v>
       </c>
       <c r="D16" t="n">
-        <v>422</v>
+        <v>500</v>
       </c>
     </row>
     <row r="18">
@@ -707,10 +707,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="D18" t="n">
-        <v>109</v>
+        <v>154</v>
       </c>
     </row>
     <row r="19">
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="D19" t="n">
-        <v>137</v>
+        <v>179</v>
       </c>
     </row>
     <row r="20">
@@ -743,10 +743,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>66</v>
+        <v>97</v>
       </c>
       <c r="D20" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="21">
@@ -756,10 +756,10 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>269</v>
+        <v>343</v>
       </c>
       <c r="D21" t="n">
-        <v>343</v>
+        <v>473</v>
       </c>
     </row>
     <row r="23">
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>956</v>
+        <v>974</v>
       </c>
       <c r="D23" t="n">
-        <v>974</v>
+        <v>1186</v>
       </c>
     </row>
   </sheetData>
@@ -786,7 +786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -802,12 +802,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>26/07</t>
+          <t>02/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>02/08</t>
+          <t>09/08</t>
         </is>
       </c>
     </row>
@@ -823,10 +823,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="n">
         <v>4</v>
-      </c>
-      <c r="D3" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -877,10 +877,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
@@ -895,10 +895,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
@@ -913,10 +913,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="D8" t="n">
-        <v>21</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9">
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D9" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
@@ -967,10 +967,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
@@ -985,10 +985,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D11" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1003,10 +1003,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D12" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
@@ -1021,23 +1021,41 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>Shemen</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Samuel Agyei</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C14" t="n">
-        <v>87</v>
-      </c>
-      <c r="D14" t="n">
+      <c r="C15" t="n">
         <v>109</v>
+      </c>
+      <c r="D15" t="n">
+        <v>154</v>
       </c>
     </row>
   </sheetData>
@@ -1067,12 +1085,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>26/07</t>
+          <t>02/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>02/08</t>
+          <t>09/08</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1109,7 @@
         <v>22</v>
       </c>
       <c r="D2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3">
@@ -1124,10 +1142,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5">
@@ -1142,10 +1160,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="D5" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6">
@@ -1155,10 +1173,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="D6" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -1172,7 +1190,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1188,12 +1206,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>26/07</t>
+          <t>02/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>02/08</t>
+          <t>09/08</t>
         </is>
       </c>
     </row>
@@ -1209,10 +1227,10 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
         <v>3</v>
-      </c>
-      <c r="D2" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -1245,7 +1263,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -1254,37 +1272,37 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Encephal College of Health</t>
+          <t>Galilea</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Samuel Tigah</t>
+          <t>Lady Vanessa Osei</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Galilea</t>
+          <t>GCTU Koinonia Governorship</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Lady Vanessa Osei</t>
+          <t>Christabel Tukpeyi</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1299,10 +1317,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -1320,7 +1338,7 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
@@ -1335,10 +1353,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -1353,28 +1371,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="D10" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Kings/Regent</t>
+          <t>Kings University</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Prince Forson</t>
+          <t>Samuel Tigah</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D11" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1389,23 +1407,41 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>Regent University</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Prince Forson</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>13</v>
+      </c>
+      <c r="D13" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C13" t="n">
-        <v>110</v>
-      </c>
-      <c r="D13" t="n">
+      <c r="C14" t="n">
         <v>104</v>
+      </c>
+      <c r="D14" t="n">
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -1435,12 +1471,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>26/07</t>
+          <t>02/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>02/08</t>
+          <t>09/08</t>
         </is>
       </c>
     </row>
@@ -1456,10 +1492,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -1474,10 +1510,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -1492,10 +1528,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
@@ -1510,10 +1546,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6">
@@ -1528,10 +1564,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
@@ -1546,10 +1582,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -1564,10 +1600,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
@@ -1582,10 +1618,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
@@ -1600,10 +1636,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -1618,10 +1654,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12">
@@ -1636,10 +1672,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D12" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13">
@@ -1654,10 +1690,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D13" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14">
@@ -1675,7 +1711,7 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
@@ -1708,10 +1744,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17">
@@ -1721,10 +1757,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="D17" t="n">
-        <v>137</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -1754,12 +1790,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>26/07</t>
+          <t>02/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>02/08</t>
+          <t>09/08</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1814,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3">
@@ -1793,10 +1829,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -1829,10 +1865,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6">
@@ -1847,10 +1883,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -1865,10 +1901,10 @@
         </is>
       </c>
       <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
         <v>3</v>
-      </c>
-      <c r="D7" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -1883,10 +1919,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -1901,10 +1937,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
@@ -1919,7 +1955,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -1937,10 +1973,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D11" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1955,10 +1991,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
@@ -1973,7 +2009,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D13" t="n">
         <v>14</v>
@@ -1991,10 +2027,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D14" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15">
@@ -2009,10 +2045,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16">
@@ -2027,10 +2063,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D16" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
@@ -2045,10 +2081,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2058,10 +2094,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>97</v>
       </c>
       <c r="D18" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -2091,12 +2127,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>26/07</t>
+          <t>02/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>02/08</t>
+          <t>09/08</t>
         </is>
       </c>
     </row>
@@ -2112,10 +2148,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -2133,7 +2169,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -2151,7 +2187,7 @@
         <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
@@ -2169,7 +2205,7 @@
         <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -2184,10 +2220,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
@@ -2202,10 +2238,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
@@ -2223,7 +2259,7 @@
         <v>25</v>
       </c>
       <c r="D8" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9">
@@ -2241,7 +2277,7 @@
         <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10">
@@ -2256,7 +2292,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -2269,10 +2305,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D11" t="n">
-        <v>74</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -2302,12 +2338,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>26/07</t>
+          <t>02/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>02/08</t>
+          <t>09/08</t>
         </is>
       </c>
     </row>
@@ -2323,10 +2359,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -2341,10 +2377,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -2362,7 +2398,7 @@
         <v>14</v>
       </c>
       <c r="D4" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5">
@@ -2413,10 +2449,10 @@
         </is>
       </c>
       <c r="C7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D7" t="n">
         <v>11</v>
-      </c>
-      <c r="D7" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -2431,10 +2467,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9">
@@ -2449,10 +2485,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -2480,10 +2516,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="D11" t="n">
-        <v>52</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -2513,12 +2549,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>26/07</t>
+          <t>02/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>02/08</t>
+          <t>09/08</t>
         </is>
       </c>
     </row>
@@ -2534,10 +2570,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
@@ -2552,7 +2588,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
         <v>3</v>
@@ -2570,7 +2606,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -2583,10 +2619,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -2616,12 +2652,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>26/07</t>
+          <t>02/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>02/08</t>
+          <t>09/08</t>
         </is>
       </c>
     </row>
@@ -2658,7 +2694,7 @@
         <v>21</v>
       </c>
       <c r="D3" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
@@ -2691,7 +2727,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
         <v>8</v>
@@ -2709,10 +2745,10 @@
         </is>
       </c>
       <c r="C6" t="n">
+        <v>11</v>
+      </c>
+      <c r="D6" t="n">
         <v>9</v>
-      </c>
-      <c r="D6" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="7">
@@ -2745,10 +2781,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="D8" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
@@ -2763,10 +2799,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D9" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
@@ -2781,10 +2817,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D10" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
@@ -2802,7 +2838,7 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -2812,10 +2848,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="D12" t="n">
-        <v>82</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -2845,12 +2881,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>26/07</t>
+          <t>02/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>02/08</t>
+          <t>09/08</t>
         </is>
       </c>
     </row>
@@ -2866,10 +2902,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D2" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -2884,10 +2920,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -2938,10 +2974,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D6" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
@@ -2956,10 +2992,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -2969,10 +3005,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="D8" t="n">
-        <v>53</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -3002,12 +3038,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>26/07</t>
+          <t>02/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>02/08</t>
+          <t>09/08</t>
         </is>
       </c>
     </row>
@@ -3023,10 +3059,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -3041,10 +3077,10 @@
         </is>
       </c>
       <c r="C3" t="n">
+        <v>9</v>
+      </c>
+      <c r="D3" t="n">
         <v>33</v>
-      </c>
-      <c r="D3" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="4">
@@ -3059,10 +3095,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
@@ -3072,10 +3108,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="D5" t="n">
-        <v>18</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -3105,12 +3141,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>26/07</t>
+          <t>02/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>02/08</t>
+          <t>09/08</t>
         </is>
       </c>
     </row>
@@ -3144,10 +3180,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -3162,10 +3198,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
@@ -3180,10 +3216,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -3198,10 +3234,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
@@ -3216,7 +3252,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D7" t="n">
         <v>8</v>
@@ -3229,10 +3265,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D8" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -3262,12 +3298,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>26/07</t>
+          <t>02/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>02/08</t>
+          <t>09/08</t>
         </is>
       </c>
     </row>
@@ -3311,12 +3347,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>26/07</t>
+          <t>02/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>02/08</t>
+          <t>09/08</t>
         </is>
       </c>
     </row>
@@ -3368,10 +3404,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -3381,10 +3417,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D5" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3414,12 +3450,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>26/07</t>
+          <t>02/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>02/08</t>
+          <t>09/08</t>
         </is>
       </c>
     </row>
@@ -3435,7 +3471,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D2" t="n">
         <v>12</v>
@@ -3456,7 +3492,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
@@ -3471,10 +3507,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
@@ -3489,10 +3525,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="D5" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -3507,10 +3543,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D6" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
@@ -3525,10 +3561,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D7" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8">
@@ -3543,10 +3579,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
@@ -3561,10 +3597,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D9" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
@@ -3579,10 +3615,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D10" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
@@ -3597,10 +3633,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
@@ -3610,10 +3646,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>124</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>

--- a/Sunday_Arrivals.xlsx
+++ b/Sunday_Arrivals.xlsx
@@ -444,12 +444,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>02/08</t>
+          <t>09/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>09/08</t>
+          <t>16/08</t>
         </is>
       </c>
     </row>
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
@@ -483,10 +483,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="D3" t="n">
-        <v>63</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4">
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="D4" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5">
@@ -519,10 +519,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="D5" t="n">
-        <v>57</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6">
@@ -537,10 +537,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D6" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D7" t="n">
-        <v>213</v>
+        <v>205</v>
       </c>
     </row>
     <row r="9">
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -604,10 +604,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
-        <v>131</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12">
@@ -622,10 +622,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="D12" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13">
@@ -640,10 +640,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>104</v>
+        <v>78</v>
       </c>
       <c r="D13" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14">
@@ -658,10 +658,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>74</v>
+        <v>116</v>
       </c>
       <c r="D14" t="n">
-        <v>116</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>52</v>
+        <v>100</v>
       </c>
       <c r="D15" t="n">
-        <v>100</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16">
@@ -689,10 +689,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>422</v>
+        <v>500</v>
       </c>
       <c r="D16" t="n">
-        <v>500</v>
+        <v>382</v>
       </c>
     </row>
     <row r="18">
@@ -707,10 +707,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>109</v>
+        <v>154</v>
       </c>
       <c r="D18" t="n">
-        <v>154</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>137</v>
+        <v>179</v>
       </c>
       <c r="D19" t="n">
-        <v>179</v>
+        <v>133</v>
       </c>
     </row>
     <row r="20">
@@ -743,10 +743,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
       <c r="D20" t="n">
-        <v>140</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21">
@@ -756,10 +756,10 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>343</v>
+        <v>473</v>
       </c>
       <c r="D21" t="n">
-        <v>473</v>
+        <v>262</v>
       </c>
     </row>
     <row r="23">
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>974</v>
+        <v>1186</v>
       </c>
       <c r="D23" t="n">
-        <v>1186</v>
+        <v>849</v>
       </c>
     </row>
   </sheetData>
@@ -802,12 +802,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>02/08</t>
+          <t>09/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>09/08</t>
+          <t>16/08</t>
         </is>
       </c>
     </row>
@@ -823,10 +823,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -877,10 +877,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -895,10 +895,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -913,10 +913,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="D7" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="D8" t="n">
-        <v>49</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
         <v>8</v>
@@ -967,10 +967,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -985,10 +985,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
@@ -1003,10 +1003,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D12" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -1021,7 +1021,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>109</v>
+        <v>154</v>
       </c>
       <c r="D15" t="n">
-        <v>154</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -1085,12 +1085,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>02/08</t>
+          <t>09/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>09/08</t>
+          <t>16/08</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D2" t="n">
         <v>24</v>
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="D4" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5">
@@ -1160,10 +1160,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6">
@@ -1173,10 +1173,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="D6" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -1206,12 +1206,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>02/08</t>
+          <t>09/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>09/08</t>
+          <t>16/08</t>
         </is>
       </c>
     </row>
@@ -1227,10 +1227,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -1248,7 +1248,7 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -1266,7 +1266,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
@@ -1281,10 +1281,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D5" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
@@ -1317,10 +1317,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -1335,10 +1335,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
@@ -1353,10 +1353,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1371,10 +1371,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -1407,10 +1407,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D12" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1425,10 +1425,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D13" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
@@ -1438,10 +1438,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>104</v>
+        <v>78</v>
       </c>
       <c r="D14" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -1455,7 +1455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1471,12 +1471,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>02/08</t>
+          <t>09/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>09/08</t>
+          <t>16/08</t>
         </is>
       </c>
     </row>
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D3" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -1528,10 +1528,10 @@
         </is>
       </c>
       <c r="C4" t="n">
+        <v>14</v>
+      </c>
+      <c r="D4" t="n">
         <v>12</v>
-      </c>
-      <c r="D4" t="n">
-        <v>14</v>
       </c>
     </row>
     <row r="5">
@@ -1546,187 +1546,187 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D5" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Block B Annex New</t>
+          <t>Block A Beta</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kevin Brown</t>
+          <t>Gracy Wellington</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Commonwealth</t>
+          <t>Block B Annex New</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Peter Tefuttor</t>
+          <t>Kevin Brown</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Diamond Jubilee New</t>
+          <t>Commonwealth</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Emelda Antwi-Agyei</t>
+          <t>Peter Tefuttor</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Evandy</t>
+          <t>Diamond Jubilee New</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Delali Apedu</t>
+          <t>Emelda Antwi-Agyei</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Evandy Annex New</t>
+          <t>Evandy</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Caroline Hammond</t>
+          <t>Delali Apedu</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Pent B</t>
+          <t>Evandy Annex New</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Yves Mensah</t>
+          <t>Caroline Hammond</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Pent C</t>
+          <t>Pent B</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Roland Cudjoe</t>
+          <t>Yves Mensah</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D12" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Pent Old &amp; A</t>
+          <t>Pent C</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Nana Kofi Danso-Mensah</t>
+          <t>Roland Cudjoe</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D13" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TF Annex New</t>
+          <t>Pent Old &amp; A</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Samuel Boateng</t>
+          <t>Nana Kofi Danso-Mensah</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="D14" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Volta</t>
+          <t>TF Annex New</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Stephanie Seglah</t>
+          <t>Samuel Boateng</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -1735,32 +1735,50 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Volta Annex New</t>
+          <t>Volta</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Esllah Osei</t>
+          <t>Stephanie Seglah</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>Volta Annex New</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Esllah Osei</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>15</v>
+      </c>
+      <c r="D17" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C17" t="n">
-        <v>137</v>
-      </c>
-      <c r="D17" t="n">
+      <c r="C18" t="n">
         <v>179</v>
+      </c>
+      <c r="D18" t="n">
+        <v>133</v>
       </c>
     </row>
   </sheetData>
@@ -1790,12 +1808,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>02/08</t>
+          <t>09/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>09/08</t>
+          <t>16/08</t>
         </is>
       </c>
     </row>
@@ -1811,10 +1829,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="D2" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -1829,7 +1847,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -1865,10 +1883,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="D5" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -1883,10 +1901,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -1901,10 +1919,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1919,7 +1937,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
         <v>2</v>
@@ -1937,10 +1955,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
@@ -1973,7 +1991,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -1991,10 +2009,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D12" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -2012,7 +2030,7 @@
         <v>14</v>
       </c>
       <c r="D13" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -2027,10 +2045,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D14" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15">
@@ -2045,10 +2063,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16">
@@ -2063,10 +2081,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -2081,7 +2099,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -2094,10 +2112,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
       <c r="D18" t="n">
-        <v>140</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -2127,12 +2145,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>02/08</t>
+          <t>09/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>09/08</t>
+          <t>16/08</t>
         </is>
       </c>
     </row>
@@ -2148,10 +2166,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -2166,10 +2184,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -2184,10 +2202,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
@@ -2202,10 +2220,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -2220,10 +2238,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -2238,10 +2256,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="D7" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -2256,10 +2274,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="D8" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9">
@@ -2274,10 +2292,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D9" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
@@ -2295,7 +2313,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -2305,10 +2323,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>74</v>
+        <v>116</v>
       </c>
       <c r="D11" t="n">
-        <v>116</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -2338,12 +2356,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>02/08</t>
+          <t>09/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>09/08</t>
+          <t>16/08</t>
         </is>
       </c>
     </row>
@@ -2359,10 +2377,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
@@ -2377,10 +2395,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D3" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
@@ -2395,10 +2413,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="D4" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
@@ -2449,10 +2467,10 @@
         </is>
       </c>
       <c r="C7" t="n">
+        <v>11</v>
+      </c>
+      <c r="D7" t="n">
         <v>6</v>
-      </c>
-      <c r="D7" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="8">
@@ -2467,10 +2485,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="D8" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
@@ -2485,10 +2503,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
@@ -2516,10 +2534,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>52</v>
+        <v>100</v>
       </c>
       <c r="D11" t="n">
-        <v>100</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -2549,12 +2567,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>02/08</t>
+          <t>09/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>09/08</t>
+          <t>16/08</t>
         </is>
       </c>
     </row>
@@ -2570,10 +2588,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
@@ -2591,7 +2609,7 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -2619,10 +2637,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -2652,12 +2670,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>02/08</t>
+          <t>09/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>09/08</t>
+          <t>16/08</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2694,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -2691,10 +2709,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
@@ -2730,7 +2748,7 @@
         <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -2745,10 +2763,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
@@ -2781,10 +2799,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D8" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
@@ -2799,10 +2817,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -2817,10 +2835,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -2835,10 +2853,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
@@ -2848,10 +2866,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="D12" t="n">
-        <v>63</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -2881,12 +2899,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>02/08</t>
+          <t>09/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>09/08</t>
+          <t>16/08</t>
         </is>
       </c>
     </row>
@@ -2902,10 +2920,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
@@ -2920,10 +2938,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -2941,7 +2959,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -2974,10 +2992,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D6" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -2992,10 +3010,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -3005,10 +3023,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="D8" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -3038,12 +3056,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>02/08</t>
+          <t>09/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>09/08</t>
+          <t>16/08</t>
         </is>
       </c>
     </row>
@@ -3059,10 +3077,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -3077,10 +3095,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="D3" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
@@ -3095,10 +3113,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
@@ -3108,10 +3126,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="D5" t="n">
-        <v>57</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -3141,12 +3159,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>02/08</t>
+          <t>09/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>09/08</t>
+          <t>16/08</t>
         </is>
       </c>
     </row>
@@ -3180,10 +3198,10 @@
         </is>
       </c>
       <c r="C3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D3" t="n">
         <v>7</v>
-      </c>
-      <c r="D3" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -3198,7 +3216,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
         <v>12</v>
@@ -3216,7 +3234,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
         <v>9</v>
@@ -3234,10 +3252,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -3255,7 +3273,7 @@
         <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -3265,10 +3283,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D8" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -3298,12 +3316,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>02/08</t>
+          <t>09/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>09/08</t>
+          <t>16/08</t>
         </is>
       </c>
     </row>
@@ -3347,12 +3365,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>02/08</t>
+          <t>09/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>09/08</t>
+          <t>16/08</t>
         </is>
       </c>
     </row>
@@ -3404,10 +3422,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -3417,10 +3435,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -3450,12 +3468,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>02/08</t>
+          <t>09/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>09/08</t>
+          <t>16/08</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3492,7 @@
         <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -3489,10 +3507,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -3507,10 +3525,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5">
@@ -3525,10 +3543,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
@@ -3543,10 +3561,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -3561,10 +3579,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D7" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
@@ -3579,7 +3597,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D8" t="n">
         <v>12</v>
@@ -3597,10 +3615,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D9" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
@@ -3615,10 +3633,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -3633,10 +3651,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
@@ -3646,10 +3664,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>

--- a/Sunday_Arrivals.xlsx
+++ b/Sunday_Arrivals.xlsx
@@ -444,12 +444,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>09/08</t>
+          <t>16/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>16/08</t>
+          <t>23/08</t>
         </is>
       </c>
     </row>
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
@@ -483,10 +483,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>63</v>
+        <v>91</v>
       </c>
       <c r="D3" t="n">
-        <v>91</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4">
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="C4" t="n">
+        <v>39</v>
+      </c>
+      <c r="D4" t="n">
         <v>31</v>
-      </c>
-      <c r="D4" t="n">
-        <v>25</v>
       </c>
     </row>
     <row r="5">
@@ -519,10 +519,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="D5" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6">
@@ -537,10 +537,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="D6" t="n">
-        <v>36</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="D7" t="n">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="9">
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -604,10 +604,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>104</v>
       </c>
       <c r="D11" t="n">
-        <v>104</v>
+        <v>154</v>
       </c>
     </row>
     <row r="12">
@@ -622,10 +622,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D12" t="n">
-        <v>71</v>
+        <v>84</v>
       </c>
     </row>
     <row r="13">
@@ -640,10 +640,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="D13" t="n">
-        <v>72</v>
+        <v>112</v>
       </c>
     </row>
     <row r="14">
@@ -658,10 +658,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>116</v>
+        <v>72</v>
       </c>
       <c r="D14" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16">
@@ -689,10 +689,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>500</v>
+        <v>382</v>
       </c>
       <c r="D16" t="n">
-        <v>382</v>
+        <v>486</v>
       </c>
     </row>
     <row r="18">
@@ -707,10 +707,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>154</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>54</v>
+        <v>97</v>
       </c>
     </row>
     <row r="19">
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>179</v>
+        <v>133</v>
       </c>
       <c r="D19" t="n">
-        <v>133</v>
+        <v>140</v>
       </c>
     </row>
     <row r="20">
@@ -743,10 +743,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>140</v>
+        <v>75</v>
       </c>
       <c r="D20" t="n">
-        <v>75</v>
+        <v>125</v>
       </c>
     </row>
     <row r="21">
@@ -756,10 +756,10 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>473</v>
+        <v>262</v>
       </c>
       <c r="D21" t="n">
-        <v>262</v>
+        <v>362</v>
       </c>
     </row>
     <row r="23">
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1186</v>
+        <v>863</v>
       </c>
       <c r="D23" t="n">
-        <v>849</v>
+        <v>1050</v>
       </c>
     </row>
   </sheetData>
@@ -802,12 +802,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>09/08</t>
+          <t>16/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>16/08</t>
+          <t>23/08</t>
         </is>
       </c>
     </row>
@@ -823,10 +823,10 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
         <v>9</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
@@ -877,10 +877,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -913,10 +913,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="D8" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9">
@@ -952,7 +952,7 @@
         <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -967,10 +967,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
@@ -985,10 +985,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
@@ -1003,10 +1003,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13">
@@ -1024,7 +1024,7 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>154</v>
+        <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>54</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -1085,12 +1085,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>09/08</t>
+          <t>16/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>16/08</t>
+          <t>23/08</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
         <v>24</v>
       </c>
       <c r="D2" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3">
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
@@ -1160,10 +1160,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D5" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6">
@@ -1173,10 +1173,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D6" t="n">
-        <v>71</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -1206,12 +1206,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>09/08</t>
+          <t>16/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>16/08</t>
+          <t>23/08</t>
         </is>
       </c>
     </row>
@@ -1227,10 +1227,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -1263,10 +1263,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -1281,10 +1281,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D5" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6">
@@ -1302,7 +1302,7 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
@@ -1317,10 +1317,10 @@
         </is>
       </c>
       <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
         <v>4</v>
-      </c>
-      <c r="D7" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -1335,10 +1335,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D8" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
@@ -1353,10 +1353,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -1371,10 +1371,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11">
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -1407,10 +1407,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13">
@@ -1425,10 +1425,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D13" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14">
@@ -1438,10 +1438,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="D14" t="n">
-        <v>72</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>09/08</t>
+          <t>16/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>16/08</t>
+          <t>23/08</t>
         </is>
       </c>
     </row>
@@ -1492,7 +1492,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
         <v>9</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
@@ -1528,10 +1528,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
@@ -1546,7 +1546,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
         <v>6</v>
@@ -1564,10 +1564,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -1582,10 +1582,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -1603,7 +1603,7 @@
         <v>13</v>
       </c>
       <c r="D8" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
@@ -1618,10 +1618,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
@@ -1636,10 +1636,10 @@
         </is>
       </c>
       <c r="C10" t="n">
+        <v>10</v>
+      </c>
+      <c r="D10" t="n">
         <v>8</v>
-      </c>
-      <c r="D10" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -1654,10 +1654,10 @@
         </is>
       </c>
       <c r="C11" t="n">
+        <v>9</v>
+      </c>
+      <c r="D11" t="n">
         <v>5</v>
-      </c>
-      <c r="D11" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="12">
@@ -1675,7 +1675,7 @@
         <v>13</v>
       </c>
       <c r="D12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14">
@@ -1708,10 +1708,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -1762,10 +1762,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18">
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>179</v>
+        <v>133</v>
       </c>
       <c r="D18" t="n">
-        <v>133</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -1808,12 +1808,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>09/08</t>
+          <t>16/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>16/08</t>
+          <t>23/08</t>
         </is>
       </c>
     </row>
@@ -1829,10 +1829,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -1901,10 +1901,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1919,10 +1919,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -1940,7 +1940,7 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
         <v>6</v>
@@ -1994,7 +1994,7 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12">
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="C13" t="n">
+        <v>5</v>
+      </c>
+      <c r="D13" t="n">
         <v>14</v>
-      </c>
-      <c r="D13" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -2045,10 +2045,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15">
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D15" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17">
@@ -2102,7 +2102,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18">
@@ -2112,10 +2112,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>140</v>
+        <v>75</v>
       </c>
       <c r="D18" t="n">
-        <v>75</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -2145,12 +2145,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>09/08</t>
+          <t>16/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>16/08</t>
+          <t>23/08</t>
         </is>
       </c>
     </row>
@@ -2166,10 +2166,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -2184,7 +2184,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -2202,10 +2202,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
@@ -2220,10 +2220,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -2238,10 +2238,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -2256,10 +2256,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -2274,10 +2274,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D8" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9">
@@ -2292,7 +2292,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D9" t="n">
         <v>11</v>
@@ -2310,10 +2310,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -2323,10 +2323,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>116</v>
+        <v>72</v>
       </c>
       <c r="D11" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -2356,12 +2356,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>09/08</t>
+          <t>16/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>16/08</t>
+          <t>23/08</t>
         </is>
       </c>
     </row>
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D2" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -2395,10 +2395,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
@@ -2467,10 +2467,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -2485,10 +2485,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
@@ -2503,10 +2503,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
@@ -2534,10 +2534,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="D11" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -2567,12 +2567,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>09/08</t>
+          <t>16/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>16/08</t>
+          <t>23/08</t>
         </is>
       </c>
     </row>
@@ -2588,10 +2588,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
@@ -2606,7 +2606,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -2637,10 +2637,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D5" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>09/08</t>
+          <t>16/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>16/08</t>
+          <t>23/08</t>
         </is>
       </c>
     </row>
@@ -2691,10 +2691,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -2709,10 +2709,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D3" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -2745,10 +2745,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -2763,10 +2763,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
@@ -2799,10 +2799,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
@@ -2817,10 +2817,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="C10" t="n">
+        <v>10</v>
+      </c>
+      <c r="D10" t="n">
         <v>9</v>
-      </c>
-      <c r="D10" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -2853,10 +2853,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>63</v>
+        <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>91</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -2899,12 +2899,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>09/08</t>
+          <t>16/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>16/08</t>
+          <t>23/08</t>
         </is>
       </c>
     </row>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D2" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
@@ -2938,10 +2938,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -2956,10 +2956,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -2992,10 +2992,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -3010,10 +3010,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -3023,10 +3023,10 @@
         </is>
       </c>
       <c r="C8" t="n">
+        <v>39</v>
+      </c>
+      <c r="D8" t="n">
         <v>31</v>
-      </c>
-      <c r="D8" t="n">
-        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -3056,12 +3056,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>09/08</t>
+          <t>16/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>16/08</t>
+          <t>23/08</t>
         </is>
       </c>
     </row>
@@ -3077,7 +3077,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -3095,10 +3095,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="D3" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4">
@@ -3113,10 +3113,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5">
@@ -3126,10 +3126,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="D5" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -3159,12 +3159,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>09/08</t>
+          <t>16/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>16/08</t>
+          <t>23/08</t>
         </is>
       </c>
     </row>
@@ -3198,10 +3198,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
@@ -3219,7 +3219,7 @@
         <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -3237,7 +3237,7 @@
         <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -3252,10 +3252,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
@@ -3270,10 +3270,10 @@
         </is>
       </c>
       <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
         <v>8</v>
-      </c>
-      <c r="D7" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -3283,10 +3283,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="D8" t="n">
-        <v>36</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -3316,12 +3316,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>09/08</t>
+          <t>16/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>16/08</t>
+          <t>23/08</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>09/08</t>
+          <t>16/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>16/08</t>
+          <t>23/08</t>
         </is>
       </c>
     </row>
@@ -3407,7 +3407,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -3422,10 +3422,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -3435,10 +3435,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -3468,12 +3468,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>09/08</t>
+          <t>16/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>16/08</t>
+          <t>23/08</t>
         </is>
       </c>
     </row>
@@ -3489,10 +3489,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
@@ -3507,10 +3507,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -3525,10 +3525,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D4" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5">
@@ -3543,10 +3543,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D5" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6">
@@ -3561,10 +3561,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
@@ -3579,10 +3579,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8">
@@ -3600,7 +3600,7 @@
         <v>12</v>
       </c>
       <c r="D8" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D9" t="n">
         <v>15</v>
@@ -3633,7 +3633,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D10" t="n">
         <v>10</v>
@@ -3651,10 +3651,10 @@
         </is>
       </c>
       <c r="C11" t="n">
+        <v>10</v>
+      </c>
+      <c r="D11" t="n">
         <v>8</v>
-      </c>
-      <c r="D11" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="12">
@@ -3664,10 +3664,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>131</v>
+        <v>104</v>
       </c>
       <c r="D12" t="n">
-        <v>104</v>
+        <v>154</v>
       </c>
     </row>
   </sheetData>

--- a/Sunday_Arrivals.xlsx
+++ b/Sunday_Arrivals.xlsx
@@ -444,12 +444,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>16/08</t>
+          <t>23/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>23/08</t>
+          <t>30/08</t>
         </is>
       </c>
     </row>
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
@@ -483,10 +483,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>91</v>
+        <v>66</v>
       </c>
       <c r="D3" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4">
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="D4" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5">
@@ -519,10 +519,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D5" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6">
@@ -537,10 +537,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="D6" t="n">
-        <v>56</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>219</v>
+        <v>202</v>
       </c>
       <c r="D7" t="n">
-        <v>202</v>
+        <v>225</v>
       </c>
     </row>
     <row r="9">
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
         <v>2</v>
@@ -604,10 +604,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>104</v>
+        <v>154</v>
       </c>
       <c r="D11" t="n">
-        <v>154</v>
+        <v>120</v>
       </c>
     </row>
     <row r="12">
@@ -622,10 +622,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="D12" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13">
@@ -640,10 +640,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>112</v>
       </c>
       <c r="D13" t="n">
-        <v>112</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -658,10 +658,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D14" t="n">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>60</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16">
@@ -689,10 +689,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>382</v>
+        <v>486</v>
       </c>
       <c r="D16" t="n">
-        <v>486</v>
+        <v>413</v>
       </c>
     </row>
     <row r="18">
@@ -707,10 +707,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>54</v>
+        <v>97</v>
       </c>
       <c r="D18" t="n">
-        <v>97</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19">
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="D19" t="n">
-        <v>140</v>
+        <v>107</v>
       </c>
     </row>
     <row r="20">
@@ -743,10 +743,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>75</v>
+        <v>125</v>
       </c>
       <c r="D20" t="n">
-        <v>125</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21">
@@ -756,10 +756,10 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>262</v>
+        <v>362</v>
       </c>
       <c r="D21" t="n">
-        <v>362</v>
+        <v>219</v>
       </c>
     </row>
     <row r="23">
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>863</v>
+        <v>1050</v>
       </c>
       <c r="D23" t="n">
-        <v>1050</v>
+        <v>857</v>
       </c>
     </row>
   </sheetData>
@@ -802,12 +802,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>16/08</t>
+          <t>23/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>23/08</t>
+          <t>30/08</t>
         </is>
       </c>
     </row>
@@ -823,10 +823,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -841,7 +841,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -877,10 +877,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -913,10 +913,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="C8" t="n">
+        <v>25</v>
+      </c>
+      <c r="D8" t="n">
         <v>15</v>
-      </c>
-      <c r="D8" t="n">
-        <v>25</v>
       </c>
     </row>
     <row r="9">
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
         <v>8</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -967,10 +967,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -985,10 +985,10 @@
         </is>
       </c>
       <c r="C11" t="n">
+        <v>11</v>
+      </c>
+      <c r="D11" t="n">
         <v>6</v>
-      </c>
-      <c r="D11" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="12">
@@ -1003,10 +1003,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D12" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>97</v>
       </c>
       <c r="D15" t="n">
-        <v>97</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -1085,12 +1085,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>16/08</t>
+          <t>23/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>23/08</t>
+          <t>30/08</t>
         </is>
       </c>
     </row>
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="D2" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3">
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D4" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5">
@@ -1160,10 +1160,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D5" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">
@@ -1173,10 +1173,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="D6" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -1206,12 +1206,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>16/08</t>
+          <t>23/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>23/08</t>
+          <t>30/08</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
         <v>8</v>
@@ -1245,7 +1245,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -1263,7 +1263,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -1281,10 +1281,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D5" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6">
@@ -1299,10 +1299,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1317,7 +1317,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
         <v>4</v>
@@ -1335,10 +1335,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D8" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9">
@@ -1353,10 +1353,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -1371,10 +1371,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11">
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="C11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" t="n">
         <v>4</v>
-      </c>
-      <c r="D11" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -1407,10 +1407,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
@@ -1425,10 +1425,10 @@
         </is>
       </c>
       <c r="C13" t="n">
+        <v>13</v>
+      </c>
+      <c r="D13" t="n">
         <v>8</v>
-      </c>
-      <c r="D13" t="n">
-        <v>13</v>
       </c>
     </row>
     <row r="14">
@@ -1438,10 +1438,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>72</v>
+        <v>112</v>
       </c>
       <c r="D14" t="n">
-        <v>112</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>16/08</t>
+          <t>23/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>23/08</t>
+          <t>30/08</t>
         </is>
       </c>
     </row>
@@ -1495,7 +1495,7 @@
         <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -1528,10 +1528,10 @@
         </is>
       </c>
       <c r="C4" t="n">
+        <v>16</v>
+      </c>
+      <c r="D4" t="n">
         <v>12</v>
-      </c>
-      <c r="D4" t="n">
-        <v>16</v>
       </c>
     </row>
     <row r="5">
@@ -1549,7 +1549,7 @@
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -1564,7 +1564,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
         <v>3</v>
@@ -1582,10 +1582,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
@@ -1600,10 +1600,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -1618,10 +1618,10 @@
         </is>
       </c>
       <c r="C9" t="n">
+        <v>8</v>
+      </c>
+      <c r="D9" t="n">
         <v>5</v>
-      </c>
-      <c r="D9" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="10">
@@ -1636,7 +1636,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D10" t="n">
         <v>8</v>
@@ -1654,10 +1654,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -1672,10 +1672,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D12" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="C13" t="n">
+        <v>13</v>
+      </c>
+      <c r="D13" t="n">
         <v>10</v>
-      </c>
-      <c r="D13" t="n">
-        <v>13</v>
       </c>
     </row>
     <row r="14">
@@ -1708,10 +1708,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D14" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1762,10 +1762,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18">
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="D18" t="n">
-        <v>140</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -1808,12 +1808,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>16/08</t>
+          <t>23/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>23/08</t>
+          <t>30/08</t>
         </is>
       </c>
     </row>
@@ -1829,10 +1829,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -1850,7 +1850,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -1919,10 +1919,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -1937,10 +1937,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1958,7 +1958,7 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="D11" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D13" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -2045,10 +2045,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D14" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17">
@@ -2099,10 +2099,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D17" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -2112,10 +2112,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>75</v>
+        <v>125</v>
       </c>
       <c r="D18" t="n">
-        <v>125</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -2145,12 +2145,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>16/08</t>
+          <t>23/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>23/08</t>
+          <t>30/08</t>
         </is>
       </c>
     </row>
@@ -2166,10 +2166,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -2202,10 +2202,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5">
@@ -2220,7 +2220,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
         <v>8</v>
@@ -2238,10 +2238,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -2256,10 +2256,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -2274,10 +2274,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9">
@@ -2295,7 +2295,7 @@
         <v>11</v>
       </c>
       <c r="D9" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
@@ -2310,10 +2310,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -2323,10 +2323,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D11" t="n">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -2340,7 +2340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>16/08</t>
+          <t>23/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>23/08</t>
+          <t>30/08</t>
         </is>
       </c>
     </row>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Papa Kojo Amoakwa</t>
+          <t>Herbert Aidoo</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -2386,66 +2386,66 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>UMC Allos 2</t>
+          <t>UMC Allos 10</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Herbert Aidoo</t>
+          <t>Doreen Nartey</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>UMC Allos 3</t>
+          <t>UMC Allos 2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Jessica Adonu</t>
+          <t>Papa Kojo Amoakwa</t>
         </is>
       </c>
       <c r="C4" t="n">
+        <v>9</v>
+      </c>
+      <c r="D4" t="n">
         <v>11</v>
-      </c>
-      <c r="D4" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>UMC Allos 4</t>
+          <t>UMC Allos 3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Linda Tunkum</t>
+          <t>Jessica Adonu</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>UMC Allos 5</t>
+          <t>UMC Allos 4</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Joshua Agymang</t>
+          <t>Linda Tunkum</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -2458,61 +2458,61 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>UMC Allos 6</t>
+          <t>UMC Allos 5</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>David Abuaku</t>
+          <t>Joshua Agymang</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>UMC Allos 7</t>
+          <t>UMC Allos 6</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Blessing Umukoro</t>
+          <t>David Abuaku</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D8" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>UMC Allos 8</t>
+          <t>UMC Allos 7</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Divine Olubakinde</t>
+          <t>Blessing Umukoro</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>UMC Allos 9</t>
+          <t>UMC Allos 8</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2530,14 +2530,50 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>UMC Allos 9</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Nancy Kubi</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>UMC E-Church</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Divine Olubakinde</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>9</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C11" t="n">
-        <v>59</v>
-      </c>
-      <c r="D11" t="n">
+      <c r="C13" t="n">
         <v>60</v>
+      </c>
+      <c r="D13" t="n">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -2567,12 +2603,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>16/08</t>
+          <t>23/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>23/08</t>
+          <t>30/08</t>
         </is>
       </c>
     </row>
@@ -2588,10 +2624,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -2609,7 +2645,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -2637,10 +2673,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D5" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -2670,12 +2706,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>16/08</t>
+          <t>23/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>23/08</t>
+          <t>30/08</t>
         </is>
       </c>
     </row>
@@ -2691,10 +2727,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -2709,10 +2745,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -2745,7 +2781,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
         <v>6</v>
@@ -2763,10 +2799,10 @@
         </is>
       </c>
       <c r="C6" t="n">
+        <v>10</v>
+      </c>
+      <c r="D6" t="n">
         <v>15</v>
-      </c>
-      <c r="D6" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="7">
@@ -2799,7 +2835,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D8" t="n">
         <v>14</v>
@@ -2817,10 +2853,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
@@ -2835,10 +2871,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -2853,7 +2889,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -2866,10 +2902,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>66</v>
       </c>
       <c r="D12" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -2899,12 +2935,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>16/08</t>
+          <t>23/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>23/08</t>
+          <t>30/08</t>
         </is>
       </c>
     </row>
@@ -2920,10 +2956,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D2" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -2938,7 +2974,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -2956,10 +2992,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -2992,10 +3028,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
@@ -3010,10 +3046,10 @@
         </is>
       </c>
       <c r="C7" t="n">
+        <v>10</v>
+      </c>
+      <c r="D7" t="n">
         <v>4</v>
-      </c>
-      <c r="D7" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -3023,10 +3059,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="D8" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -3056,12 +3092,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>16/08</t>
+          <t>23/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>23/08</t>
+          <t>30/08</t>
         </is>
       </c>
     </row>
@@ -3080,7 +3116,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -3095,10 +3131,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D3" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
@@ -3113,10 +3149,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D4" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
@@ -3126,10 +3162,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D5" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -3143,7 +3179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3159,12 +3195,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>16/08</t>
+          <t>23/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>23/08</t>
+          <t>30/08</t>
         </is>
       </c>
     </row>
@@ -3176,14 +3212,14 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Princess Gueyennevievarl Wilson-Anderson</t>
+          <t>Sheryl Azu</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -3198,10 +3234,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D3" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
@@ -3216,10 +3252,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
@@ -3234,10 +3270,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
@@ -3252,10 +3288,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
@@ -3270,23 +3306,41 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>Wisconsin Haatso</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Amanda Tenu</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C8" t="n">
-        <v>36</v>
-      </c>
-      <c r="D8" t="n">
+      <c r="C9" t="n">
         <v>56</v>
+      </c>
+      <c r="D9" t="n">
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -3316,12 +3370,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>16/08</t>
+          <t>23/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>23/08</t>
+          <t>30/08</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3419,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>16/08</t>
+          <t>23/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>23/08</t>
+          <t>30/08</t>
         </is>
       </c>
     </row>
@@ -3404,10 +3458,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -3422,10 +3476,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -3435,7 +3489,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
         <v>2</v>
@@ -3468,12 +3522,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>16/08</t>
+          <t>23/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>23/08</t>
+          <t>30/08</t>
         </is>
       </c>
     </row>
@@ -3489,10 +3543,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -3507,10 +3561,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -3525,10 +3579,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="D4" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5">
@@ -3543,10 +3597,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D5" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
@@ -3561,10 +3615,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
@@ -3579,10 +3633,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D7" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8">
@@ -3597,10 +3651,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D8" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
@@ -3636,7 +3690,7 @@
         <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -3651,7 +3705,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D11" t="n">
         <v>8</v>
@@ -3664,10 +3718,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>154</v>
       </c>
       <c r="D12" t="n">
-        <v>154</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
